--- a/Parcial 1/Talleres/G4_Matriz_IREB_VNº1_SGA.xlsx
+++ b/Parcial 1/Talleres/G4_Matriz_IREB_VNº1_SGA.xlsx
@@ -361,7 +361,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="105">
   <si>
     <t>MATRIZ PARA COMPROBACIÓN REQUERIMIENTOS DE CALIDAD DE PROYECTO ACADEMICO</t>
   </si>
@@ -410,11 +410,6 @@
     <t>1. Aceptacion del docente y cliente</t>
   </si>
   <si>
-    <t>1. Videoconferencia de la entrevista
-2. Minuta de la entrevista
-3. Aceptación por videoconferencia</t>
-  </si>
-  <si>
     <t>Ranked</t>
   </si>
   <si>
@@ -445,7 +440,7 @@
     <t>Valid and up-to date</t>
   </si>
   <si>
-    <t>1. No se implementaron las correcciones realizadas tanto por la docente, y no hubo revisión de la versión final con el cliente.              
+    <t>1. Se implementaron las correcciones realizadas por la docente        
 2. El SRS cuenta con control de versiones</t>
   </si>
   <si>
@@ -1003,7 +998,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1057,9 +1052,6 @@
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="12" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="7" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -2274,8 +2266,8 @@
       <c r="J9" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="23" t="s">
-        <v>14</v>
+      <c r="K9" s="20" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" ht="66.0" customHeight="1">
@@ -2283,26 +2275,26 @@
         <v>2.0</v>
       </c>
       <c r="C10" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="7"/>
+      <c r="E10" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="24" t="s">
+      <c r="F10" s="24" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="G10" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="G10" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="25" t="s">
+      <c r="J10" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="24" t="s">
         <v>18</v>
-      </c>
-      <c r="J10" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="25" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" ht="66.0" customHeight="1">
@@ -2310,26 +2302,26 @@
         <v>3.0</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="25" t="s">
-        <v>21</v>
+      <c r="F11" s="24" t="s">
+        <v>20</v>
       </c>
       <c r="G11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="25" t="s">
-        <v>22</v>
+      <c r="I11" s="24" t="s">
+        <v>21</v>
       </c>
       <c r="J11" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="25" t="s">
-        <v>23</v>
+      <c r="K11" s="24" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" ht="66.0" customHeight="1">
@@ -2337,26 +2329,26 @@
         <v>4.0</v>
       </c>
       <c r="C12" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="7"/>
+      <c r="E12" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="25" t="s">
         <v>24</v>
-      </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="26" t="s">
-        <v>25</v>
       </c>
       <c r="G12" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="26" t="s">
-        <v>26</v>
+      <c r="I12" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="J12" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="26" t="s">
-        <v>27</v>
+      <c r="K12" s="25" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" ht="75.0" customHeight="1">
@@ -2364,53 +2356,53 @@
         <v>5.0</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="26" t="s">
-        <v>29</v>
+      <c r="F13" s="25" t="s">
+        <v>28</v>
       </c>
       <c r="G13" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="26" t="s">
-        <v>30</v>
+      <c r="I13" s="25" t="s">
+        <v>29</v>
       </c>
       <c r="J13" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="26" t="s">
-        <v>31</v>
+      <c r="K13" s="25" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="66.0" customHeight="1">
       <c r="B14" s="17">
         <v>6.0</v>
       </c>
-      <c r="C14" s="27" t="s">
-        <v>32</v>
+      <c r="C14" s="26" t="s">
+        <v>31</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="26" t="s">
-        <v>33</v>
+      <c r="F14" s="25" t="s">
+        <v>32</v>
       </c>
       <c r="G14" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="26" t="s">
-        <v>34</v>
+      <c r="I14" s="25" t="s">
+        <v>33</v>
       </c>
       <c r="J14" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="26" t="s">
-        <v>35</v>
+      <c r="K14" s="25" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15" ht="66.0" customHeight="1">
@@ -2418,26 +2410,26 @@
         <v>7.0</v>
       </c>
       <c r="C15" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="7"/>
+      <c r="E15" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="26" t="s">
+      <c r="G15" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I15" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="26" t="s">
+      <c r="J15" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K15" s="25" t="s">
         <v>38</v>
-      </c>
-      <c r="J15" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="K15" s="26" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" ht="66.0" customHeight="1">
@@ -2445,26 +2437,26 @@
         <v>8.0</v>
       </c>
       <c r="C16" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="7"/>
+      <c r="E16" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="26" t="s">
+      <c r="G16" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="25" t="s">
         <v>41</v>
       </c>
-      <c r="G16" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="26" t="s">
+      <c r="J16" s="23" t="s">
+        <v>15</v>
+      </c>
+      <c r="K16" s="25" t="s">
         <v>42</v>
-      </c>
-      <c r="J16" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" s="26" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="17" ht="77.25" customHeight="1">
@@ -2472,26 +2464,26 @@
         <v>9.0</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="29" t="s">
-        <v>45</v>
+      <c r="F17" s="28" t="s">
+        <v>44</v>
       </c>
       <c r="G17" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="25" t="s">
-        <v>46</v>
+      <c r="I17" s="24" t="s">
+        <v>45</v>
       </c>
       <c r="J17" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K17" s="29" t="s">
-        <v>47</v>
+      <c r="K17" s="28" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="18" ht="71.25" customHeight="1">
@@ -2499,26 +2491,26 @@
         <v>10.0</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="7"/>
       <c r="E18" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="26" t="s">
-        <v>49</v>
+      <c r="F18" s="25" t="s">
+        <v>48</v>
       </c>
       <c r="G18" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="26" t="s">
-        <v>50</v>
+      <c r="I18" s="25" t="s">
+        <v>49</v>
       </c>
       <c r="J18" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K18" s="26" t="s">
-        <v>51</v>
+      <c r="K18" s="25" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="19" ht="66.0" customHeight="1">
@@ -2526,26 +2518,26 @@
         <v>11.0</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="26" t="s">
-        <v>53</v>
+      <c r="F19" s="25" t="s">
+        <v>52</v>
       </c>
       <c r="G19" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="26" t="s">
-        <v>54</v>
+      <c r="I19" s="25" t="s">
+        <v>53</v>
       </c>
       <c r="J19" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="K19" s="26" t="s">
-        <v>55</v>
+      <c r="K19" s="25" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="20" ht="14.25" customHeight="1">
@@ -3981,191 +3973,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31" t="s">
+      <c r="A1" s="29"/>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="B2" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="C2" s="33">
+        <v>46126.0</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="B3" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="34">
-        <v>46126.0</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="33" t="s">
+      <c r="C3" s="34" t="s">
         <v>58</v>
       </c>
-      <c r="C3" s="35" t="s">
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="B4" s="32" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="33" t="s">
+      <c r="C4" s="34" t="s">
         <v>60</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="30.75" customHeight="1">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" ht="30.75" customHeight="1">
+      <c r="A7" s="36" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="B7" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="C7" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="D7" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="39" t="s">
+    </row>
+    <row r="8" ht="30.75" customHeight="1">
+      <c r="A8" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B8" s="40" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="41" t="s">
+      <c r="C8" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" ht="30.75" customHeight="1">
+      <c r="A9" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="43"/>
-    </row>
-    <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="41" t="s">
+      <c r="C9" s="43" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="44"/>
+    </row>
+    <row r="10" ht="30.75" customHeight="1">
+      <c r="A10" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="44" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="45"/>
-    </row>
-    <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="41" t="s">
+      <c r="C10" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="42"/>
+    </row>
+    <row r="11" ht="30.75" customHeight="1">
+      <c r="A11" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="B11" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="43"/>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B11" s="41" t="s">
+      <c r="C11" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="42"/>
+    </row>
+    <row r="12" ht="30.75" customHeight="1">
+      <c r="A12" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="B12" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="43"/>
-    </row>
-    <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="41" t="s">
+      <c r="C12" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="42"/>
+    </row>
+    <row r="13" ht="30.75" customHeight="1">
+      <c r="A13" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="43"/>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="B13" s="41" t="s">
+      <c r="C13" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="42"/>
+    </row>
+    <row r="14" ht="30.75" customHeight="1">
+      <c r="A14" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="B14" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="43"/>
-    </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="B14" s="41" t="s">
+      <c r="C14" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="42"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="B15" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="43"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="40">
-        <v>8.0</v>
-      </c>
-      <c r="B15" s="41" t="s">
+      <c r="C15" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="42"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="45">
+        <v>9.0</v>
+      </c>
+      <c r="B16" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="43"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="46">
-        <v>9.0</v>
-      </c>
-      <c r="B16" s="47" t="s">
+      <c r="C16" s="47"/>
+      <c r="D16" s="47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" ht="20.25" customHeight="1">
+      <c r="A17" s="48" t="s">
         <v>76</v>
-      </c>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" ht="20.25" customHeight="1">
-      <c r="A17" s="49" t="s">
-        <v>77</v>
       </c>
       <c r="C17" s="22">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$8:$C$16)</f>
@@ -4177,109 +4169,109 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="50">
+      <c r="A18" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="49">
         <f t="shared" ref="C18:D18" si="1">C17/9</f>
         <v>0.8888888889</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="49">
         <f t="shared" si="1"/>
         <v>0.1111111111</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="22"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+    </row>
+    <row r="21" ht="20.25" customHeight="1">
+      <c r="A21" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="32.25" customHeight="1">
+      <c r="A22" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B22" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-    </row>
-    <row r="21" ht="20.25" customHeight="1">
-      <c r="A21" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" ht="32.25" customHeight="1">
-      <c r="A22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="41" t="s">
+      <c r="C22" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="42"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="43"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="41" t="s">
+      <c r="C23" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="42"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="B24" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="43"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="41" t="s">
+      <c r="C24" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="42"/>
+    </row>
+    <row r="25" ht="34.5" customHeight="1">
+      <c r="A25" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="B25" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="43"/>
-    </row>
-    <row r="25" ht="34.5" customHeight="1">
-      <c r="A25" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="41" t="s">
+      <c r="C25" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="42"/>
+    </row>
+    <row r="26" ht="40.5" customHeight="1">
+      <c r="A26" s="45">
+        <v>5.0</v>
+      </c>
+      <c r="B26" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="43"/>
-    </row>
-    <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="46">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="57"/>
+      <c r="C26" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="56"/>
     </row>
     <row r="27" ht="24.75" customHeight="1">
-      <c r="A27" s="49" t="s">
-        <v>77</v>
+      <c r="A27" s="48" t="s">
+        <v>76</v>
       </c>
       <c r="C27" s="22">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$22:$C$26)</f>
@@ -4291,82 +4283,82 @@
       </c>
     </row>
     <row r="28" ht="28.5" customHeight="1">
-      <c r="A28" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="50">
+      <c r="A28" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="49">
         <f t="shared" ref="C28:D28" si="2">C27/5</f>
         <v>1</v>
       </c>
-      <c r="D28" s="50">
+      <c r="D28" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="49"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="22"/>
     </row>
     <row r="30" ht="24.0" customHeight="1">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" ht="24.0" customHeight="1">
+      <c r="A31" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" ht="37.5" customHeight="1">
+      <c r="A32" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B32" s="40" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="31" ht="24.0" customHeight="1">
-      <c r="A31" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" ht="37.5" customHeight="1">
-      <c r="A32" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B32" s="41" t="s">
+      <c r="C32" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="47"/>
+    </row>
+    <row r="33" ht="37.5" customHeight="1">
+      <c r="A33" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B33" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="48"/>
-    </row>
-    <row r="33" ht="37.5" customHeight="1">
-      <c r="A33" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B33" s="41" t="s">
+      <c r="C33" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="47"/>
+    </row>
+    <row r="34" ht="37.5" customHeight="1">
+      <c r="A34" s="45">
+        <v>3.0</v>
+      </c>
+      <c r="B34" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="48"/>
-    </row>
-    <row r="34" ht="37.5" customHeight="1">
-      <c r="A34" s="46">
-        <v>3.0</v>
-      </c>
-      <c r="B34" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="48"/>
-      <c r="D34" s="58" t="s">
-        <v>68</v>
+      <c r="C34" s="47"/>
+      <c r="D34" s="57" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="35" ht="24.0" customHeight="1">
-      <c r="A35" s="49" t="s">
-        <v>77</v>
+      <c r="A35" s="48" t="s">
+        <v>76</v>
       </c>
       <c r="C35" s="22">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$32:$C$34)</f>
@@ -4378,14 +4370,14 @@
       </c>
     </row>
     <row r="36" ht="24.0" customHeight="1">
-      <c r="A36" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="50">
+      <c r="A36" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="49">
         <f t="shared" ref="C36:D36" si="3">C35/3</f>
         <v>0.6666666667</v>
       </c>
-      <c r="D36" s="50">
+      <c r="D36" s="49">
         <f t="shared" si="3"/>
         <v>0.3333333333</v>
       </c>
@@ -4394,31 +4386,31 @@
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="58" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="B41" s="29" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="30" t="s">
-        <v>90</v>
       </c>
       <c r="C41" s="22">
         <v>89.0</v>
       </c>
     </row>
     <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="30" t="s">
-        <v>79</v>
+      <c r="B42" s="29" t="s">
+        <v>78</v>
       </c>
       <c r="C42" s="22">
         <v>100.0</v>
       </c>
     </row>
     <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="60">
+      <c r="B43" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="59">
         <v>67.0</v>
       </c>
     </row>
@@ -5468,191 +5460,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31" t="s">
+      <c r="A1" s="29"/>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+    </row>
+    <row r="2" ht="14.25" customHeight="1">
+      <c r="B2" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="C2" s="33">
+        <v>46126.0</v>
+      </c>
+    </row>
+    <row r="3" ht="14.25" customHeight="1">
+      <c r="B3" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="34">
-        <v>46126.0</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" ht="14.25" customHeight="1">
+      <c r="B4" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="30.75" customHeight="1">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" ht="30.75" customHeight="1">
+      <c r="A7" s="36" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="B7" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="C7" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="D7" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="39" t="s">
+    </row>
+    <row r="8" ht="30.75" customHeight="1">
+      <c r="A8" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B8" s="40" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="41" t="s">
+      <c r="C8" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" ht="30.75" customHeight="1">
+      <c r="A9" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="43"/>
-    </row>
-    <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="41" t="s">
+      <c r="C9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="42"/>
+    </row>
+    <row r="10" ht="30.75" customHeight="1">
+      <c r="A10" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="43"/>
-    </row>
-    <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="41" t="s">
+      <c r="C10" s="41"/>
+      <c r="D10" s="47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" ht="30.75" customHeight="1">
+      <c r="A11" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="B11" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="42"/>
-      <c r="D10" s="48" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B11" s="41" t="s">
+      <c r="C11" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="42"/>
+    </row>
+    <row r="12" ht="30.75" customHeight="1">
+      <c r="A12" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="B12" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="43"/>
-    </row>
-    <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="41" t="s">
+      <c r="C12" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="42"/>
+    </row>
+    <row r="13" ht="30.75" customHeight="1">
+      <c r="A13" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="43"/>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="B13" s="41" t="s">
+      <c r="C13" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="42"/>
+    </row>
+    <row r="14" ht="30.75" customHeight="1">
+      <c r="A14" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="B14" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="43"/>
-    </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="B14" s="41" t="s">
+      <c r="C14" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="42"/>
+    </row>
+    <row r="15" ht="44.25" customHeight="1">
+      <c r="A15" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="B15" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="43"/>
-    </row>
-    <row r="15" ht="44.25" customHeight="1">
-      <c r="A15" s="40">
-        <v>8.0</v>
-      </c>
-      <c r="B15" s="41" t="s">
+      <c r="C15" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="42"/>
+    </row>
+    <row r="16" ht="64.5" customHeight="1">
+      <c r="A16" s="45">
+        <v>9.0</v>
+      </c>
+      <c r="B16" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="43"/>
-    </row>
-    <row r="16" ht="64.5" customHeight="1">
-      <c r="A16" s="46">
-        <v>9.0</v>
-      </c>
-      <c r="B16" s="47" t="s">
+      <c r="C16" s="47"/>
+      <c r="D16" s="47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" ht="20.25" customHeight="1">
+      <c r="A17" s="48" t="s">
         <v>76</v>
-      </c>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" ht="20.25" customHeight="1">
-      <c r="A17" s="49" t="s">
-        <v>77</v>
       </c>
       <c r="C17" s="22">
         <f>COUNTA('Hoja 1'!$C$8:$C$16)</f>
@@ -5664,109 +5656,109 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="50">
+      <c r="A18" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="49">
         <f t="shared" ref="C18:D18" si="1">C17/9</f>
         <v>0.7777777778</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="49">
         <f t="shared" si="1"/>
         <v>0.2222222222</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="22"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+    </row>
+    <row r="21" ht="20.25" customHeight="1">
+      <c r="A21" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="32.25" customHeight="1">
+      <c r="A22" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B22" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-    </row>
-    <row r="21" ht="20.25" customHeight="1">
-      <c r="A21" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" ht="32.25" customHeight="1">
-      <c r="A22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="41" t="s">
+      <c r="C22" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="42"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="43"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="41" t="s">
+      <c r="C23" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="42"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="B24" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="43"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="41" t="s">
+      <c r="C24" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="42"/>
+    </row>
+    <row r="25" ht="34.5" customHeight="1">
+      <c r="A25" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="B25" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="43"/>
-    </row>
-    <row r="25" ht="34.5" customHeight="1">
-      <c r="A25" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="41" t="s">
+      <c r="C25" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="42"/>
+    </row>
+    <row r="26" ht="40.5" customHeight="1">
+      <c r="A26" s="45">
+        <v>5.0</v>
+      </c>
+      <c r="B26" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="43"/>
-    </row>
-    <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="46">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="57"/>
+      <c r="C26" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="56"/>
     </row>
     <row r="27" ht="24.75" customHeight="1">
-      <c r="A27" s="49" t="s">
-        <v>77</v>
+      <c r="A27" s="48" t="s">
+        <v>76</v>
       </c>
       <c r="C27" s="22">
         <f>COUNTA('Hoja 1'!$C$22:$C$26)</f>
@@ -5778,82 +5770,82 @@
       </c>
     </row>
     <row r="28" ht="28.5" customHeight="1">
-      <c r="A28" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="50">
+      <c r="A28" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="49">
         <f t="shared" ref="C28:D28" si="2">C27/5</f>
         <v>1</v>
       </c>
-      <c r="D28" s="50">
+      <c r="D28" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="49"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="22"/>
     </row>
     <row r="30" ht="24.0" customHeight="1">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" ht="24.0" customHeight="1">
+      <c r="A31" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" ht="37.5" customHeight="1">
+      <c r="A32" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B32" s="40" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="31" ht="24.0" customHeight="1">
-      <c r="A31" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" ht="37.5" customHeight="1">
-      <c r="A32" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B32" s="41" t="s">
+      <c r="C32" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="47"/>
+    </row>
+    <row r="33" ht="37.5" customHeight="1">
+      <c r="A33" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B33" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="48"/>
-    </row>
-    <row r="33" ht="37.5" customHeight="1">
-      <c r="A33" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B33" s="41" t="s">
+      <c r="C33" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="47"/>
+    </row>
+    <row r="34" ht="37.5" customHeight="1">
+      <c r="A34" s="45">
+        <v>3.0</v>
+      </c>
+      <c r="B34" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="48"/>
-    </row>
-    <row r="34" ht="37.5" customHeight="1">
-      <c r="A34" s="46">
-        <v>3.0</v>
-      </c>
-      <c r="B34" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D34" s="48"/>
+      <c r="C34" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="47"/>
     </row>
     <row r="35" ht="24.0" customHeight="1">
-      <c r="A35" s="49" t="s">
-        <v>77</v>
+      <c r="A35" s="48" t="s">
+        <v>76</v>
       </c>
       <c r="C35" s="22">
         <f>COUNTA('Hoja 1'!$C$32:$C$34)</f>
@@ -5865,14 +5857,14 @@
       </c>
     </row>
     <row r="36" ht="24.0" customHeight="1">
-      <c r="A36" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="50">
+      <c r="A36" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="49">
         <f t="shared" ref="C36:D36" si="3">C35/3</f>
         <v>1</v>
       </c>
-      <c r="D36" s="50">
+      <c r="D36" s="49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5881,29 +5873,29 @@
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="58" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="B41" s="29" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="30" t="s">
-        <v>90</v>
       </c>
       <c r="C41" s="22">
         <v>89.0</v>
       </c>
     </row>
     <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="30" t="s">
-        <v>79</v>
+      <c r="B42" s="29" t="s">
+        <v>78</v>
       </c>
       <c r="C42" s="22">
         <v>100.0</v>
       </c>
     </row>
     <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="30" t="s">
-        <v>85</v>
+      <c r="B43" s="29" t="s">
+        <v>84</v>
       </c>
       <c r="C43" s="22">
         <v>100.0</v>
@@ -6955,191 +6947,191 @@
   </cols>
   <sheetData>
     <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31" t="s">
+      <c r="A1" s="29"/>
+      <c r="B1" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="32" t="s">
+      <c r="C1" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="29"/>
+      <c r="L1" s="29"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="29"/>
+      <c r="R1" s="29"/>
+      <c r="S1" s="29"/>
+      <c r="T1" s="29"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+    </row>
+    <row r="2" ht="17.25" customHeight="1">
+      <c r="B2" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="30"/>
-      <c r="I1" s="30"/>
-      <c r="J1" s="30"/>
-      <c r="K1" s="30"/>
-      <c r="L1" s="30"/>
-      <c r="M1" s="30"/>
-      <c r="N1" s="30"/>
-      <c r="O1" s="30"/>
-      <c r="P1" s="30"/>
-      <c r="Q1" s="30"/>
-      <c r="R1" s="30"/>
-      <c r="S1" s="30"/>
-      <c r="T1" s="30"/>
-      <c r="U1" s="30"/>
-      <c r="V1" s="30"/>
-      <c r="W1" s="30"/>
-      <c r="X1" s="30"/>
-      <c r="Y1" s="30"/>
-      <c r="Z1" s="30"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="C2" s="33">
+        <v>46126.0</v>
+      </c>
+    </row>
+    <row r="3" ht="20.25" customHeight="1">
+      <c r="B3" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="C2" s="34">
-        <v>46126.0</v>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="B3" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>93</v>
+      <c r="C3" s="34" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="B4" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="35" t="s">
+      <c r="B4" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>
     <row r="6" ht="30.75" customHeight="1">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="35" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" ht="30.75" customHeight="1">
+      <c r="A7" s="36" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="B7" s="37" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="C7" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="D7" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="39" t="s">
+    </row>
+    <row r="8" ht="30.75" customHeight="1">
+      <c r="A8" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B8" s="40" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="41" t="s">
+      <c r="C8" s="41" t="s">
         <v>67</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="D8" s="42"/>
+    </row>
+    <row r="9" ht="30.75" customHeight="1">
+      <c r="A9" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B9" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="D8" s="43"/>
-    </row>
-    <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="41" t="s">
+      <c r="C9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" s="42"/>
+    </row>
+    <row r="10" ht="41.25" customHeight="1">
+      <c r="A10" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="B10" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="43"/>
-    </row>
-    <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="41" t="s">
+      <c r="C10" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" s="42"/>
+    </row>
+    <row r="11" ht="30.75" customHeight="1">
+      <c r="A11" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="B11" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="C10" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="43"/>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B11" s="41" t="s">
+      <c r="C11" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" s="42"/>
+    </row>
+    <row r="12" ht="30.75" customHeight="1">
+      <c r="A12" s="39">
+        <v>5.0</v>
+      </c>
+      <c r="B12" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="43"/>
-    </row>
-    <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="40">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="41" t="s">
+      <c r="C12" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D12" s="42"/>
+    </row>
+    <row r="13" ht="30.75" customHeight="1">
+      <c r="A13" s="39">
+        <v>6.0</v>
+      </c>
+      <c r="B13" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D12" s="43"/>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="40">
-        <v>6.0</v>
-      </c>
-      <c r="B13" s="41" t="s">
+      <c r="C13" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="42"/>
+    </row>
+    <row r="14" ht="30.75" customHeight="1">
+      <c r="A14" s="39">
+        <v>7.0</v>
+      </c>
+      <c r="B14" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="C13" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" s="43"/>
-    </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="40">
-        <v>7.0</v>
-      </c>
-      <c r="B14" s="41" t="s">
+      <c r="C14" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="42"/>
+    </row>
+    <row r="15" ht="30.75" customHeight="1">
+      <c r="A15" s="39">
+        <v>8.0</v>
+      </c>
+      <c r="B15" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="43"/>
-    </row>
-    <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="40">
-        <v>8.0</v>
-      </c>
-      <c r="B15" s="41" t="s">
+      <c r="C15" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="42"/>
+    </row>
+    <row r="16" ht="54.75" customHeight="1">
+      <c r="A16" s="45">
+        <v>9.0</v>
+      </c>
+      <c r="B16" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C15" s="42" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="43"/>
-    </row>
-    <row r="16" ht="54.75" customHeight="1">
-      <c r="A16" s="46">
-        <v>9.0</v>
-      </c>
-      <c r="B16" s="47" t="s">
+      <c r="C16" s="47"/>
+      <c r="D16" s="47" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" ht="20.25" customHeight="1">
+      <c r="A17" s="48" t="s">
         <v>76</v>
-      </c>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" ht="20.25" customHeight="1">
-      <c r="A17" s="49" t="s">
-        <v>77</v>
       </c>
       <c r="C17" s="22">
         <f>COUNTA('Hoja 2'!$C$8:$C$16)</f>
@@ -7151,109 +7143,109 @@
       </c>
     </row>
     <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C18" s="50">
+      <c r="A18" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C18" s="49">
         <f t="shared" ref="C18:D18" si="1">C17/9</f>
         <v>0.8888888889</v>
       </c>
-      <c r="D18" s="50">
+      <c r="D18" s="49">
         <f t="shared" si="1"/>
         <v>0.1111111111</v>
       </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="49"/>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
+      <c r="A19" s="48"/>
+      <c r="B19" s="48"/>
+      <c r="C19" s="49"/>
       <c r="D19" s="22"/>
     </row>
     <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="51" t="s">
+      <c r="A20" s="50" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" s="51"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="51"/>
+    </row>
+    <row r="21" ht="20.25" customHeight="1">
+      <c r="A21" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B21" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="32.25" customHeight="1">
+      <c r="A22" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B22" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-    </row>
-    <row r="21" ht="20.25" customHeight="1">
-      <c r="A21" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D21" s="56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" ht="32.25" customHeight="1">
-      <c r="A22" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="41" t="s">
+      <c r="C22" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="42"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B23" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="C22" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" s="43"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="41" t="s">
+      <c r="C23" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="42"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="39">
+        <v>3.0</v>
+      </c>
+      <c r="B24" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D23" s="43"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="40">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="41" t="s">
+      <c r="C24" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D24" s="42"/>
+    </row>
+    <row r="25" ht="34.5" customHeight="1">
+      <c r="A25" s="39">
+        <v>4.0</v>
+      </c>
+      <c r="B25" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="43"/>
-    </row>
-    <row r="25" ht="34.5" customHeight="1">
-      <c r="A25" s="40">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="41" t="s">
+      <c r="C25" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D25" s="42"/>
+    </row>
+    <row r="26" ht="40.5" customHeight="1">
+      <c r="A26" s="45">
+        <v>5.0</v>
+      </c>
+      <c r="B26" s="46" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="43"/>
-    </row>
-    <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="46">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D26" s="57"/>
+      <c r="C26" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D26" s="56"/>
     </row>
     <row r="27" ht="24.75" customHeight="1">
-      <c r="A27" s="49" t="s">
-        <v>77</v>
+      <c r="A27" s="48" t="s">
+        <v>76</v>
       </c>
       <c r="C27" s="22">
         <f>COUNTA('Hoja 2'!$C$22:$C$26)</f>
@@ -7265,82 +7257,82 @@
       </c>
     </row>
     <row r="28" ht="28.5" customHeight="1">
-      <c r="A28" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C28" s="50">
+      <c r="A28" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C28" s="49">
         <f t="shared" ref="C28:D28" si="2">C27/5</f>
         <v>1</v>
       </c>
-      <c r="D28" s="50">
+      <c r="D28" s="49">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="49"/>
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
+      <c r="A29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="49"/>
       <c r="D29" s="22"/>
     </row>
     <row r="30" ht="24.0" customHeight="1">
-      <c r="A30" s="36" t="s">
+      <c r="A30" s="35" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" ht="24.0" customHeight="1">
+      <c r="A31" s="52" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="53" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="55" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" ht="37.5" customHeight="1">
+      <c r="A32" s="39">
+        <v>1.0</v>
+      </c>
+      <c r="B32" s="40" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="31" ht="24.0" customHeight="1">
-      <c r="A31" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="55" t="s">
-        <v>65</v>
-      </c>
-      <c r="D31" s="56" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" ht="37.5" customHeight="1">
-      <c r="A32" s="40">
-        <v>1.0</v>
-      </c>
-      <c r="B32" s="41" t="s">
+      <c r="C32" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="47"/>
+    </row>
+    <row r="33" ht="37.5" customHeight="1">
+      <c r="A33" s="39">
+        <v>2.0</v>
+      </c>
+      <c r="B33" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="48"/>
-    </row>
-    <row r="33" ht="37.5" customHeight="1">
-      <c r="A33" s="40">
-        <v>2.0</v>
-      </c>
-      <c r="B33" s="41" t="s">
+      <c r="C33" s="47" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="47"/>
+    </row>
+    <row r="34" ht="37.5" customHeight="1">
+      <c r="A34" s="45">
+        <v>3.0</v>
+      </c>
+      <c r="B34" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="C33" s="48" t="s">
-        <v>68</v>
-      </c>
-      <c r="D33" s="48"/>
-    </row>
-    <row r="34" ht="37.5" customHeight="1">
-      <c r="A34" s="46">
-        <v>3.0</v>
-      </c>
-      <c r="B34" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="C34" s="48"/>
-      <c r="D34" s="48" t="s">
-        <v>68</v>
+      <c r="C34" s="47"/>
+      <c r="D34" s="47" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="35" ht="24.0" customHeight="1">
-      <c r="A35" s="49" t="s">
-        <v>77</v>
+      <c r="A35" s="48" t="s">
+        <v>76</v>
       </c>
       <c r="C35" s="22">
         <f>COUNTA('Hoja 2'!$C$32:$C$34)</f>
@@ -7352,14 +7344,14 @@
       </c>
     </row>
     <row r="36" ht="24.0" customHeight="1">
-      <c r="A36" s="49" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="50">
+      <c r="A36" s="48" t="s">
+        <v>77</v>
+      </c>
+      <c r="C36" s="49">
         <f t="shared" ref="C36:D36" si="3">C35/3</f>
         <v>0.6666666667</v>
       </c>
-      <c r="D36" s="50">
+      <c r="D36" s="49">
         <f t="shared" si="3"/>
         <v>0.3333333333</v>
       </c>
@@ -7368,31 +7360,31 @@
     <row r="38" ht="14.25" customHeight="1"/>
     <row r="39" ht="14.25" customHeight="1"/>
     <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="59" t="s">
+      <c r="A40" s="58" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" ht="30.0" customHeight="1">
+      <c r="B41" s="29" t="s">
         <v>89</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="30" t="s">
-        <v>90</v>
       </c>
       <c r="C41" s="22">
         <v>89.0</v>
       </c>
     </row>
     <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="30" t="s">
-        <v>79</v>
+      <c r="B42" s="29" t="s">
+        <v>78</v>
       </c>
       <c r="C42" s="22">
         <v>100.0</v>
       </c>
     </row>
     <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="60">
+      <c r="B43" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="59">
         <v>67.0</v>
       </c>
     </row>
@@ -8440,27 +8432,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="61" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="61" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="62" t="s">
+      <c r="B2" s="62" t="s">
         <v>96</v>
-      </c>
-      <c r="B2" s="63" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="62" t="s">
         <v>98</v>
-      </c>
-      <c r="B3" s="63" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -9481,27 +9473,27 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="61" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="61" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="62" t="s">
+      <c r="B2" s="62" t="s">
         <v>96</v>
-      </c>
-      <c r="B2" s="63" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B3" s="62" t="s">
         <v>98</v>
-      </c>
-      <c r="B3" s="63" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="4" ht="14.25" customHeight="1"/>
@@ -10522,35 +10514,35 @@
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="60" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="60" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="61" t="s">
-        <v>95</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="63" t="s">
+      <c r="A2" s="62" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" s="62" t="s">
         <v>100</v>
       </c>
-      <c r="B2" s="63" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="62" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="63" t="s">
+      <c r="B3" s="62" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="63" t="s">
+    </row>
+    <row r="4" ht="44.25" customHeight="1">
+      <c r="A4" s="62" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1">
-      <c r="A4" s="63" t="s">
+      <c r="B4" s="62" t="s">
         <v>104</v>
-      </c>
-      <c r="B4" s="63" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="5" ht="14.25" customHeight="1"/>

--- a/Parcial 1/Talleres/G4_Matriz_IREB_VNº1_SGA.xlsx
+++ b/Parcial 1/Talleres/G4_Matriz_IREB_VNº1_SGA.xlsx
@@ -416,7 +416,7 @@
     <t>NOK</t>
   </si>
   <si>
-    <t>1. En el SRS se especifca que es un requisito Primario, pero los subcasos  no poseen una priorización</t>
+    <t>1. En el SRS se especifíca que es un requisito Primario, pero los subcasos  no poseen una priorización</t>
   </si>
   <si>
     <t>1.En el documento se especifica que es un requisito de tipo primario pero no se especifica que tipo de prioridad tienen</t>

--- a/Parcial 1/Talleres/G4_Matriz_IREB_VNº1_SGA.xlsx
+++ b/Parcial 1/Talleres/G4_Matriz_IREB_VNº1_SGA.xlsx
@@ -1,149 +1,329 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sjean\Desktop\Universidad ESPE\Sexto Semestre Ing.Software\ADSW\JeancarloSanti_30723_G4_ADSW\Parcial 1\Talleres\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82242E52-44E5-4A9E-A210-EED6E5C87629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Matriz Ckeck LIst" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="MODELO LISTA DE COMPROBACION - " sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="Hoja 1" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="Hoja 2" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="RECOMENDACIONES - CU001" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="RECOMENDACIONES - CU002" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="RECOMENDACIONES - CU003" sheetId="7" r:id="rId11"/>
+    <sheet name="Matriz Ckeck LIst" sheetId="1" r:id="rId1"/>
+    <sheet name="MODELO LISTA DE COMPROBACION - " sheetId="2" r:id="rId2"/>
+    <sheet name="Hoja 1" sheetId="3" r:id="rId3"/>
+    <sheet name="Hoja 2" sheetId="4" r:id="rId4"/>
+    <sheet name="RECOMENDACIONES - CU001" sheetId="5" r:id="rId5"/>
+    <sheet name="RECOMENDACIONES - CU002" sheetId="6" r:id="rId6"/>
+    <sheet name="RECOMENDACIONES - CU003" sheetId="7" r:id="rId7"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="E7">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="F7">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 La información contenida en memoria se utiliza para actualizar los campos de la base de datos.</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="G7">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="I7">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Se guarda en un archivo Excel los registros que dieron un problema en la actualización.</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="J7">
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Control del nivel de acuedo entre las partes Cliente y Desarrollador</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="K7">
+    <comment ref="K7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 jeny ruiz:
 Posterior a la actualización, se guardaran automáticamente el nombre de usuario, fecha, hora, registro antiguo, registro nuevo.</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C9">
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">jeny ruiz:
 Todos los interesados reconocen que el  requisito es correcto y relevante
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="F9">
+    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="I9">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="K9">
+    <comment ref="K9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Es importante ingresar el archivo plano en formato excel para el cliente y el desarrollador</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C10">
+    <comment ref="C10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Ponderado por importancia o prioridad</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C11">
+    <comment ref="C11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Todos los lectores comprenden de la misma manera, sólo una interpretación</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C12">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Toda nueva información  ha sido incorporada</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C13">
+    <comment ref="C13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">jeny ruiz:
 Refleja las espectativas  del implicado
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C14">
+    <comment ref="C14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">jeny ruiz:
 Sin contradicciones
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C15">
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Su cumplimiento o no cumplimiento puede der probado con un esfuerzo razonable</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C16">
+    <comment ref="C16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Puede ser implementado  y desarrollado en las condiciones actuales(tiempo, Presupuest,, orgtanizaciòn, ect)</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C17">
+    <comment ref="C17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 El origen del requisito y sus relaciones con otros requisitos  están claros.</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C18">
+    <comment ref="C18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Trata todos los asuntos relevantes</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="C19">
+    <comment ref="C19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
       <text>
-        <t xml:space="preserve">jeny ruiz:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>jeny ruiz:
 Para todos los interesados dependiendo  de la fase del proyecto podrían estar involucrados  distintos implicados,(Glosario de tèrminos)</t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -151,69 +331,141 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B8">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 COMPLETITUD DOCUMENTO</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B9">
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000002000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 COMPLETITUD REQUISITO INDIVIDUAL
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B10">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000003000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 TRAZABILIDAD</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B11">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000004000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 trazabilidad
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B12">
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000005000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 TRAZABILIDAD
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B13">
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000006000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 CORRECCION
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B14">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000007000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 CONSISTENCIA</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B15">
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000008000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 NECESIDAD
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B16">
+    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000009000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 verificable 
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -221,69 +473,141 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B8">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 COMPLETITUD DOCUMENTO</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B9">
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 COMPLETITUD REQUISITO INDIVIDUAL
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B10">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 TRAZABILIDAD</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B11">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000004000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 trazabilidad
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B12">
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000005000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 TRAZABILIDAD
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B13">
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000006000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 CORRECCION
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B14">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000007000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 CONSISTENCIA</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B15">
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000008000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 NECESIDAD
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B16">
+    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000009000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 verificable 
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -291,69 +615,141 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="B8">
+    <comment ref="B8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 COMPLETITUD DOCUMENTO</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B9">
+    <comment ref="B9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 COMPLETITUD REQUISITO INDIVIDUAL
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B10">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 TRAZABILIDAD</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B11">
+    <comment ref="B11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 trazabilidad
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B12">
+    <comment ref="B12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 TRAZABILIDAD
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B13">
+    <comment ref="B13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000006000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 CORRECCION
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B14">
+    <comment ref="B14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000007000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>ESPE:
 CONSISTENCIA</t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B15">
+    <comment ref="B15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000008000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 NECESIDAD
 </t>
+        </r>
       </text>
     </comment>
-    <comment authorId="0" ref="B16">
+    <comment ref="B16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000009000000}">
       <text>
-        <t xml:space="preserve">ESPE:
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">ESPE:
 verificable 
 </t>
+        </r>
       </text>
     </comment>
   </commentList>
@@ -361,7 +757,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="112">
   <si>
     <t>MATRIZ PARA COMPROBACIÓN REQUERIMIENTOS DE CALIDAD DE PROYECTO ACADEMICO</t>
   </si>
@@ -472,9 +868,6 @@
   </si>
   <si>
     <t xml:space="preserve">1. Los casos de uso mantienen consistencia entre sí; los estados del pago fluyen lógicamente de un RF a otro sin contradecirse.                                           </t>
-  </si>
-  <si>
-    <t>Verifiable</t>
   </si>
   <si>
     <t>1. No existen criterios por los cuales se pueda medir el cumplimiento dado que no se implementó la propuesta.</t>
@@ -688,103 +1081,130 @@
   <si>
     <t>Validar que la lógica de aplicar el pago a las deudas más antiguas y el cálculo automático del recargo del 12% reflejan exactamente el reglamento del conjunto.</t>
   </si>
+  <si>
+    <t>Verificable</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>Establecer una priorización formal para los subcasos CU-1.1 Iniciar Sesión, CU-1.2 Recuperar Contraseña y CU-1.3 Configurar Perfiles, usando un criterio uniforme como Must, Should, Could o prioridad Alta, Media, Baja.</t>
+  </si>
+  <si>
+    <t>¿El requisito es viable con los recursos, presupuesto, alcance y nivel de validación actual del proyecto?</t>
+  </si>
+  <si>
+    <t>¿Se ha definido una priorización explícita de los subcasos de uso dl requisito, indicando cuáles son obligatorios para la primera versión y cuáles pueden diferirse?</t>
+  </si>
+  <si>
+    <t>Revisar la factibilidad del requisito junto con el cliente y el equipo, delimitando una versión mínima viable. Si no existe presupuesto ni aprobación formal para toda la funcionalidad planteada, debe priorizarse una implementación mínima centrada en autenticación y acceso</t>
+  </si>
+  <si>
+    <t>¿Se han definido criterios de aceptación, resultados esperados y casos de prueba que permitan comprobar objetivamente el cumplimiento de los subcasos del requisito?</t>
+  </si>
+  <si>
+    <t>Definir criterios de aceptación medibles para cada subcaso de uso del requisito . Estos criterios deben documentarse junto con casos de prueba funcionales y resultados esperados, de forma que el requisito pueda evaluarse objetivamente durante la fase de prueba.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <fonts count="17">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8.0"/>
+      <sz val="8"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FF1F497D"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
-    <font/>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="0"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="16.0"/>
+      <sz val="16"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="14.0"/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="18.0"/>
+      <sz val="18"/>
       <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
     </font>
@@ -794,7 +1214,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -834,27 +1254,39 @@
     </fill>
   </fills>
   <borders count="17">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -864,6 +1296,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -875,22 +1308,30 @@
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
         <color rgb="FF000000"/>
       </top>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -905,6 +1346,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -913,25 +1355,33 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -944,6 +1394,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -954,6 +1405,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -966,6 +1418,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -978,6 +1431,7 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -988,277 +1442,195 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+  <cellXfs count="57">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="11" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="12" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="4" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="7" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="5" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="13" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="15" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="12" fillId="6" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="14" fillId="6" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="15" fillId="6" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="6" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="9" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="16" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="16" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="8" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="9" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="4" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="7" fillId="7" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="51">
     <dxf>
-      <font/>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
       <fill>
-        <patternFill patternType="none"/>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="0"/>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFD8D8D8"/>
-          <bgColor rgb="FFD8D8D8"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB8CCE4"/>
-          <bgColor rgb="FFB8CCE4"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="6"/>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFEAF1DD"/>
-          <bgColor rgb="FFEAF1DD"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFDE9D9"/>
-          <bgColor rgb="FFFDE9D9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFFFC7CE"/>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
     <dxf>
       <font>
@@ -1270,7 +1642,25 @@
           <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1282,7 +1672,66 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1294,7 +1743,69 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1303,61 +1814,329 @@
       <fill>
         <patternFill patternType="none"/>
       </fill>
-      <border/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFC6EFCE"/>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFC7CE"/>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDE9D9"/>
+          <bgColor rgb="FFFDE9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF1DD"/>
+          <bgColor rgb="FFEAF1DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8D8D8"/>
+          <bgColor rgb="FFD8D8D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDE9D9"/>
+          <bgColor rgb="FFFDE9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF1DD"/>
+          <bgColor rgb="FFEAF1DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8D8D8"/>
+          <bgColor rgb="FFD8D8D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFDE9D9"/>
+          <bgColor rgb="FFFDE9D9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="9"/>
+          <bgColor theme="9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFEAF1DD"/>
+          <bgColor rgb="FFEAF1DD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="6"/>
+          <bgColor theme="6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB8CCE4"/>
+          <bgColor rgb="FFB8CCE4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFD8D8D8"/>
+          <bgColor rgb="FFD8D8D8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="0"/>
+          <bgColor theme="0"/>
+        </patternFill>
+      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="9">
-    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="MODELO LISTA DE COMPROBACION - -style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
+      <tableStyleElement type="headerRow" dxfId="50"/>
+      <tableStyleElement type="firstRowStripe" dxfId="49"/>
+      <tableStyleElement type="secondRowStripe" dxfId="48"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 2">
-      <tableStyleElement dxfId="4" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="MODELO LISTA DE COMPROBACION - -style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}">
+      <tableStyleElement type="headerRow" dxfId="47"/>
+      <tableStyleElement type="firstRowStripe" dxfId="46"/>
+      <tableStyleElement type="secondRowStripe" dxfId="45"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="MODELO LISTA DE COMPROBACION - -style 3">
-      <tableStyleElement dxfId="6" type="headerRow"/>
-      <tableStyleElement dxfId="7" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="MODELO LISTA DE COMPROBACION - -style 3" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}">
+      <tableStyleElement type="headerRow" dxfId="44"/>
+      <tableStyleElement type="firstRowStripe" dxfId="43"/>
+      <tableStyleElement type="secondRowStripe" dxfId="42"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF03000000}">
+      <tableStyleElement type="headerRow" dxfId="41"/>
+      <tableStyleElement type="firstRowStripe" dxfId="40"/>
+      <tableStyleElement type="secondRowStripe" dxfId="39"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style 2">
-      <tableStyleElement dxfId="4" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF04000000}">
+      <tableStyleElement type="headerRow" dxfId="38"/>
+      <tableStyleElement type="firstRowStripe" dxfId="37"/>
+      <tableStyleElement type="secondRowStripe" dxfId="36"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 1-style 3">
-      <tableStyleElement dxfId="6" type="headerRow"/>
-      <tableStyleElement dxfId="7" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 1-style 3" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF05000000}">
+      <tableStyleElement type="headerRow" dxfId="35"/>
+      <tableStyleElement type="firstRowStripe" dxfId="34"/>
+      <tableStyleElement type="secondRowStripe" dxfId="33"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 2-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 2-style" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF06000000}">
+      <tableStyleElement type="headerRow" dxfId="32"/>
+      <tableStyleElement type="firstRowStripe" dxfId="31"/>
+      <tableStyleElement type="secondRowStripe" dxfId="30"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 2-style 2">
-      <tableStyleElement dxfId="4" type="headerRow"/>
-      <tableStyleElement dxfId="5" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 2-style 2" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF07000000}">
+      <tableStyleElement type="headerRow" dxfId="29"/>
+      <tableStyleElement type="firstRowStripe" dxfId="28"/>
+      <tableStyleElement type="secondRowStripe" dxfId="27"/>
     </tableStyle>
-    <tableStyle count="3" pivot="0" name="Hoja 2-style 3">
-      <tableStyleElement dxfId="6" type="headerRow"/>
-      <tableStyleElement dxfId="7" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+    <tableStyle name="Hoja 2-style 3" pivot="0" count="3" xr9:uid="{00000000-0011-0000-FFFF-FFFF08000000}">
+      <tableStyleElement type="headerRow" dxfId="26"/>
+      <tableStyleElement type="firstRowStripe" dxfId="25"/>
+      <tableStyleElement type="secondRowStripe" dxfId="24"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1374,7 +2153,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" i="0">
+              <a:rPr lang="en-US" b="1" i="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1389,16 +2168,27 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.3094930008748907"/>
-          <c:y val="0.06018518518518518"/>
+          <c:x val="0.30949300087489068"/>
+          <c:y val="6.0185185185185182E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:view3D>
       <c:rotX val="50"/>
-      <c:perspective val="0"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="1"/>
     </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
       <c:pie3DChart>
@@ -1408,29 +2198,54 @@
           <c:order val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-7F09-4718-AF65-E507CCA927AE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-7F09-4718-AF65-E507CCA927AE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-7F09-4718-AF65-E507CCA927AE}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1438,18 +2253,50 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'MODELO LISTA DE COMPROBACION - '!$B$41:$B$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>CONTENIDO </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DOCUMENTACIÓN</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NIVEL DE ACUERDO</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'MODELO LISTA DE COMPROBACION - '!$C$41:$C$43</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-7F09-4718-AF65-E507CCA927AE}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1458,6 +2305,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
       </c:pie3DChart>
     </c:plotArea>
@@ -1476,16 +2324,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1502,7 +2362,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" i="0">
+              <a:rPr lang="en-US" b="1" i="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1517,16 +2377,27 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.3094930008748907"/>
-          <c:y val="0.06018518518518518"/>
+          <c:x val="0.30949300087489068"/>
+          <c:y val="6.0185185185185182E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:view3D>
       <c:rotX val="50"/>
-      <c:perspective val="0"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="1"/>
     </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
       <c:pie3DChart>
@@ -1536,29 +2407,54 @@
           <c:order val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-1055-4D09-9CA5-03E04F107684}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-1055-4D09-9CA5-03E04F107684}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-1055-4D09-9CA5-03E04F107684}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1566,18 +2462,50 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Hoja 1'!$B$41:$B$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>CONTENIDO </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DOCUMENTACIÓN</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NIVEL DE ACUERDO</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Hoja 1'!$C$41:$C$43</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-1055-4D09-9CA5-03E04F107684}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1586,6 +2514,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
       </c:pie3DChart>
     </c:plotArea>
@@ -1604,16 +2533,28 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="es-ES"/>
+  <c:roundedCorners val="1"/>
+  <c:style val="2"/>
   <c:chart>
     <c:title>
       <c:tx>
@@ -1630,7 +2571,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr b="1" i="0">
+              <a:rPr lang="en-US" b="1" i="0">
                 <a:solidFill>
                   <a:srgbClr val="757575"/>
                 </a:solidFill>
@@ -1645,16 +2586,27 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.3094930008748907"/>
-          <c:y val="0.06018518518518518"/>
+          <c:x val="0.30949300087489068"/>
+          <c:y val="6.0185185185185182E-2"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
     </c:title>
+    <c:autoTitleDeleted val="0"/>
     <c:view3D>
       <c:rotX val="50"/>
-      <c:perspective val="0"/>
+      <c:rotY val="0"/>
+      <c:rAngAx val="1"/>
     </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+    </c:backWall>
     <c:plotArea>
       <c:layout/>
       <c:pie3DChart>
@@ -1664,29 +2616,54 @@
           <c:order val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="4F81BD"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-7CB8-4517-BF79-644A466B36DC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="C0504D"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-7CB8-4517-BF79-644A466B36DC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="9BBB59"/>
               </a:solidFill>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-7CB8-4517-BF79-644A466B36DC}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1694,18 +2671,50 @@
             <c:showPercent val="1"/>
             <c:showBubbleSize val="0"/>
             <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>'Hoja 2'!$B$41:$B$43</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>CONTENIDO </c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>DOCUMENTACIÓN</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NIVEL DE ACUERDO</c:v>
+                </c:pt>
+              </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Hoja 2'!$C$41:$C$43</c:f>
-              <c:numCache/>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>89</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>67</c:v>
+                </c:pt>
+              </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-7CB8-4517-BF79-644A466B36DC}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -1714,6 +2723,7 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
       </c:pie3DChart>
     </c:plotArea>
@@ -1732,20 +2742,24 @@
               <a:latin typeface="+mn-lt"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -1754,9 +2768,15 @@
       <xdr:rowOff>485775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4286250" cy="2143125"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1765,7 +2785,43 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>485775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4286250" cy="2143125"/>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1775,7 +2831,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
@@ -1784,9 +2840,15 @@
       <xdr:rowOff>485775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4286250" cy="2143125"/>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 2"/>
+        <xdr:cNvPr id="3" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
@@ -1795,7 +2857,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1804,162 +2866,120 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>485775</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4286250" cy="2143125"/>
-    <xdr:graphicFrame>
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Chart 3"/>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="A7:D16">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table_2" displayName="Table_2" ref="A21:D26">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Table_3" displayName="Table_3" ref="A31:D34">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="MODELO LISTA DE COMPROBACION - -style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="Table_4" displayName="Table_4" ref="A7:D16">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_5" name="Table_5" id="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Table_5" displayName="Table_5" ref="A21:D26">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 1-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_6" name="Table_6" id="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Table_6" displayName="Table_6" ref="A31:D34">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 1-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 1-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A7:D16" displayName="Table_7" name="Table_7" id="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Table_7" displayName="Table_7" ref="A7:D16">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 2-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 2-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A21:D26" displayName="Table_8" name="Table_8" id="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{00000000-000C-0000-FFFF-FFFF07000000}" name="Table_8" displayName="Table_8" ref="A21:D26">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0700-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0700-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0700-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0700-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 2-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 2-style 2" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A31:D34" displayName="Table_9" name="Table_9" id="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{00000000-000C-0000-FFFF-FFFF08000000}" name="Table_9" displayName="Table_9" ref="A31:D34">
   <tableColumns count="4">
-    <tableColumn name="No." id="1"/>
-    <tableColumn name="Pregunta" id="2"/>
-    <tableColumn name="SI" id="3"/>
-    <tableColumn name="NO " id="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0800-000001000000}" name="No."/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0800-000002000000}" name="Pregunta"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0800-000003000000}" name="SI"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0800-000004000000}" name="NO "/>
   </tableColumns>
-  <tableStyleInfo name="Hoja 2-style 3" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Hoja 2-style 3" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -2149,1004 +3169,1028 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:K1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="4.57"/>
-    <col customWidth="1" min="2" max="2" width="4.43"/>
-    <col customWidth="1" min="3" max="3" width="3.71"/>
-    <col customWidth="1" min="4" max="4" width="34.86"/>
-    <col customWidth="1" min="5" max="5" width="9.71"/>
-    <col customWidth="1" min="6" max="6" width="51.14"/>
-    <col customWidth="1" min="7" max="7" width="10.14"/>
-    <col customWidth="1" hidden="1" min="8" max="8" width="4.71"/>
-    <col customWidth="1" min="9" max="9" width="42.71"/>
-    <col customWidth="1" min="10" max="10" width="9.86"/>
-    <col customWidth="1" min="11" max="11" width="44.57"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
+    <col min="2" max="2" width="4.453125" customWidth="1"/>
+    <col min="3" max="3" width="3.7265625" customWidth="1"/>
+    <col min="4" max="4" width="34.81640625" customWidth="1"/>
+    <col min="5" max="5" width="9.7265625" customWidth="1"/>
+    <col min="6" max="6" width="51.08984375" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" customWidth="1"/>
+    <col min="8" max="8" width="4.7265625" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="42.7265625" customWidth="1"/>
+    <col min="10" max="10" width="9.81640625" customWidth="1"/>
+    <col min="11" max="11" width="44.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
+    <row r="1" spans="2:11" ht="14.25" customHeight="1">
       <c r="C1" s="1"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1">
+    <row r="2" spans="2:11" ht="14.25" customHeight="1">
       <c r="C2" s="1"/>
     </row>
-    <row r="3" ht="30.0" customHeight="1">
-      <c r="C3" s="2" t="s">
+    <row r="3" spans="2:11" ht="30" customHeight="1">
+      <c r="C3" s="37" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" ht="30.0" customHeight="1"/>
-    <row r="5" ht="30.0" customHeight="1">
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="38"/>
+      <c r="G3" s="38"/>
+      <c r="H3" s="38"/>
+      <c r="I3" s="38"/>
+      <c r="J3" s="38"/>
+      <c r="K3" s="38"/>
+    </row>
+    <row r="4" spans="2:11" ht="30" customHeight="1">
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="38"/>
+      <c r="H4" s="38"/>
+      <c r="I4" s="38"/>
+      <c r="J4" s="38"/>
+      <c r="K4" s="38"/>
+    </row>
+    <row r="5" spans="2:11" ht="30" customHeight="1">
       <c r="C5" s="2"/>
       <c r="D5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="39" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" ht="55.5" customHeight="1">
+      <c r="F5" s="38"/>
+      <c r="G5" s="38"/>
+      <c r="H5" s="38"/>
+      <c r="I5" s="38"/>
+      <c r="J5" s="38"/>
+      <c r="K5" s="38"/>
+    </row>
+    <row r="6" spans="2:11" ht="55.5" customHeight="1">
       <c r="C6" s="1"/>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="7"/>
-    </row>
-    <row r="7" ht="45.0" customHeight="1">
-      <c r="B7" s="8" t="s">
+      <c r="G6" s="41"/>
+      <c r="H6" s="41"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="42"/>
+    </row>
+    <row r="7" spans="2:11" ht="45" customHeight="1">
+      <c r="B7" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="10"/>
-      <c r="E7" s="11" t="s">
+      <c r="D7" s="44"/>
+      <c r="E7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="11" t="s">
+      <c r="G7" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="12" t="s">
+      <c r="H7" s="4"/>
+      <c r="I7" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="11"/>
-      <c r="K7" s="12" t="s">
+      <c r="J7" s="34"/>
+      <c r="K7" s="36" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" ht="60.0" customHeight="1">
-      <c r="B8" s="14"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-    </row>
-    <row r="9" ht="66.0" customHeight="1">
-      <c r="B9" s="17">
-        <v>1.0</v>
-      </c>
-      <c r="C9" s="18" t="s">
+    <row r="8" spans="2:11" ht="60" customHeight="1">
+      <c r="B8" s="35"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="46"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+    </row>
+    <row r="9" spans="2:11" ht="66" customHeight="1">
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="7"/>
-      <c r="E9" s="19" t="s">
+      <c r="D9" s="42"/>
+      <c r="E9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="H9" s="22"/>
-      <c r="I9" s="20" t="s">
+      <c r="H9" s="8"/>
+      <c r="I9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="21" t="s">
+      <c r="J9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="20" t="s">
+      <c r="K9" s="7" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" ht="66.0" customHeight="1">
-      <c r="B10" s="17">
-        <v>2.0</v>
-      </c>
-      <c r="C10" s="18" t="s">
+    <row r="10" spans="2:11" ht="66" customHeight="1">
+      <c r="B10" s="5">
+        <v>2</v>
+      </c>
+      <c r="C10" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="23" t="s">
+      <c r="D10" s="42"/>
+      <c r="E10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="24" t="s">
+      <c r="F10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="24" t="s">
+      <c r="I10" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="J10" s="23" t="s">
+      <c r="J10" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="10" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" ht="66.0" customHeight="1">
-      <c r="B11" s="17">
-        <v>3.0</v>
-      </c>
-      <c r="C11" s="18" t="s">
+    <row r="11" spans="2:11" ht="66" customHeight="1">
+      <c r="B11" s="5">
+        <v>3</v>
+      </c>
+      <c r="C11" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="D11" s="7"/>
-      <c r="E11" s="19" t="s">
+      <c r="D11" s="42"/>
+      <c r="E11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="J11" s="21" t="s">
+      <c r="J11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="12" ht="66.0" customHeight="1">
-      <c r="B12" s="17">
-        <v>4.0</v>
-      </c>
-      <c r="C12" s="18" t="s">
+    <row r="12" spans="2:11" ht="66" customHeight="1">
+      <c r="B12" s="5">
+        <v>4</v>
+      </c>
+      <c r="C12" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="7"/>
-      <c r="E12" s="21" t="s">
+      <c r="D12" s="42"/>
+      <c r="E12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="25" t="s">
+      <c r="I12" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K12" s="25" t="s">
+      <c r="K12" s="11" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" ht="75.0" customHeight="1">
-      <c r="B13" s="17">
-        <v>5.0</v>
-      </c>
-      <c r="C13" s="18" t="s">
+    <row r="13" spans="2:11" ht="75" customHeight="1">
+      <c r="B13" s="5">
+        <v>5</v>
+      </c>
+      <c r="C13" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="7"/>
-      <c r="E13" s="19" t="s">
+      <c r="D13" s="42"/>
+      <c r="E13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I13" s="25" t="s">
+      <c r="I13" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="J13" s="21" t="s">
+      <c r="J13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="25" t="s">
+      <c r="K13" s="11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="14" ht="66.0" customHeight="1">
-      <c r="B14" s="17">
-        <v>6.0</v>
-      </c>
-      <c r="C14" s="26" t="s">
+    <row r="14" spans="2:11" ht="66" customHeight="1">
+      <c r="B14" s="5">
+        <v>6</v>
+      </c>
+      <c r="C14" s="48" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="7"/>
-      <c r="E14" s="19" t="s">
+      <c r="D14" s="42"/>
+      <c r="E14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="G14" s="21" t="s">
+      <c r="G14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="25" t="s">
+      <c r="I14" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="J14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="15" ht="66.0" customHeight="1">
-      <c r="B15" s="17">
-        <v>7.0</v>
-      </c>
-      <c r="C15" s="18" t="s">
+    <row r="15" spans="2:11" ht="66" customHeight="1">
+      <c r="B15" s="5">
+        <v>7</v>
+      </c>
+      <c r="C15" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="D15" s="42"/>
+      <c r="E15" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="7"/>
-      <c r="E15" s="23" t="s">
+      <c r="G15" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="25" t="s">
+      <c r="I15" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="J15" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I15" s="25" t="s">
+      <c r="K15" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="J15" s="23" t="s">
+    </row>
+    <row r="16" spans="2:11" ht="66" customHeight="1">
+      <c r="B16" s="5">
+        <v>8</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="42"/>
+      <c r="E16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="K15" s="25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" ht="66.0" customHeight="1">
-      <c r="B16" s="17">
-        <v>8.0</v>
-      </c>
-      <c r="C16" s="18" t="s">
+      <c r="F16" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="7"/>
-      <c r="E16" s="23" t="s">
+      <c r="G16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="25" t="s">
+      <c r="I16" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="J16" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="I16" s="25" t="s">
+      <c r="K16" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="J16" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="K16" s="25" t="s">
+    </row>
+    <row r="17" spans="2:11" ht="77.25" customHeight="1">
+      <c r="B17" s="5">
+        <v>9</v>
+      </c>
+      <c r="C17" s="47" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="17" ht="77.25" customHeight="1">
-      <c r="B17" s="17">
-        <v>9.0</v>
-      </c>
-      <c r="C17" s="18" t="s">
+      <c r="D17" s="42"/>
+      <c r="E17" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="7"/>
-      <c r="E17" s="19" t="s">
+      <c r="G17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F17" s="28" t="s">
+      <c r="I17" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="J17" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I17" s="24" t="s">
+      <c r="K17" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="J17" s="21" t="s">
+    </row>
+    <row r="18" spans="2:11" ht="71.25" customHeight="1">
+      <c r="B18" s="5">
+        <v>10</v>
+      </c>
+      <c r="C18" s="47" t="s">
+        <v>46</v>
+      </c>
+      <c r="D18" s="42"/>
+      <c r="E18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="K17" s="28" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" ht="71.25" customHeight="1">
-      <c r="B18" s="17">
-        <v>10.0</v>
-      </c>
-      <c r="C18" s="18" t="s">
+      <c r="F18" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="7"/>
-      <c r="E18" s="19" t="s">
+      <c r="G18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F18" s="25" t="s">
+      <c r="I18" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="G18" s="21" t="s">
+      <c r="J18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="25" t="s">
+      <c r="K18" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="J18" s="21" t="s">
+    </row>
+    <row r="19" spans="2:11" ht="66" customHeight="1">
+      <c r="B19" s="5">
         <v>11</v>
       </c>
-      <c r="K18" s="25" t="s">
+      <c r="C19" s="47" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="19" ht="66.0" customHeight="1">
-      <c r="B19" s="17">
-        <v>11.0</v>
-      </c>
-      <c r="C19" s="18" t="s">
+      <c r="D19" s="42"/>
+      <c r="E19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D19" s="7"/>
-      <c r="E19" s="19" t="s">
+      <c r="G19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="F19" s="25" t="s">
+      <c r="I19" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="G19" s="21" t="s">
+      <c r="J19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="25" t="s">
+      <c r="K19" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J19" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="K19" s="25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" ht="14.25" customHeight="1">
+    </row>
+    <row r="20" spans="2:11" ht="14.25" customHeight="1">
       <c r="C20" s="1"/>
     </row>
-    <row r="21" ht="14.25" customHeight="1">
+    <row r="21" spans="2:11" ht="14.25" customHeight="1">
       <c r="C21" s="1"/>
     </row>
-    <row r="22" ht="14.25" customHeight="1">
+    <row r="22" spans="2:11" ht="14.25" customHeight="1">
       <c r="C22" s="1"/>
     </row>
-    <row r="23" ht="14.25" customHeight="1">
+    <row r="23" spans="2:11" ht="14.25" customHeight="1">
       <c r="C23" s="1"/>
     </row>
-    <row r="24" ht="14.25" customHeight="1">
+    <row r="24" spans="2:11" ht="14.25" customHeight="1">
       <c r="C24" s="1"/>
     </row>
-    <row r="25" ht="14.25" customHeight="1">
+    <row r="25" spans="2:11" ht="14.25" customHeight="1">
       <c r="C25" s="1"/>
     </row>
-    <row r="26" ht="14.25" customHeight="1">
+    <row r="26" spans="2:11" ht="14.25" customHeight="1">
       <c r="C26" s="1"/>
     </row>
-    <row r="27" ht="14.25" customHeight="1">
+    <row r="27" spans="2:11" ht="14.25" customHeight="1">
       <c r="C27" s="1"/>
     </row>
-    <row r="28" ht="14.25" customHeight="1">
+    <row r="28" spans="2:11" ht="14.25" customHeight="1">
       <c r="C28" s="1"/>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
+    <row r="29" spans="2:11" ht="14.25" customHeight="1">
       <c r="C29" s="1"/>
     </row>
-    <row r="30" ht="14.25" customHeight="1">
+    <row r="30" spans="2:11" ht="14.25" customHeight="1">
       <c r="C30" s="1"/>
     </row>
-    <row r="31" ht="14.25" customHeight="1">
+    <row r="31" spans="2:11" ht="14.25" customHeight="1">
       <c r="C31" s="1"/>
     </row>
-    <row r="32" ht="14.25" customHeight="1">
+    <row r="32" spans="2:11" ht="14.25" customHeight="1">
       <c r="C32" s="1"/>
     </row>
-    <row r="33" ht="14.25" customHeight="1">
+    <row r="33" spans="3:3" ht="14.25" customHeight="1">
       <c r="C33" s="1"/>
     </row>
-    <row r="34" ht="14.25" customHeight="1">
+    <row r="34" spans="3:3" ht="14.25" customHeight="1">
       <c r="C34" s="1"/>
     </row>
-    <row r="35" ht="14.25" customHeight="1">
+    <row r="35" spans="3:3" ht="14.25" customHeight="1">
       <c r="C35" s="1"/>
     </row>
-    <row r="36" ht="14.25" customHeight="1">
+    <row r="36" spans="3:3" ht="14.25" customHeight="1">
       <c r="C36" s="1"/>
     </row>
-    <row r="37" ht="14.25" customHeight="1">
+    <row r="37" spans="3:3" ht="14.25" customHeight="1">
       <c r="C37" s="1"/>
     </row>
-    <row r="38" ht="14.25" customHeight="1">
+    <row r="38" spans="3:3" ht="14.25" customHeight="1">
       <c r="C38" s="1"/>
     </row>
-    <row r="39" ht="14.25" customHeight="1">
+    <row r="39" spans="3:3" ht="14.25" customHeight="1">
       <c r="C39" s="1"/>
     </row>
-    <row r="40" ht="14.25" customHeight="1">
+    <row r="40" spans="3:3" ht="14.25" customHeight="1">
       <c r="C40" s="1"/>
     </row>
-    <row r="41" ht="14.25" customHeight="1">
+    <row r="41" spans="3:3" ht="14.25" customHeight="1">
       <c r="C41" s="1"/>
     </row>
-    <row r="42" ht="14.25" customHeight="1">
+    <row r="42" spans="3:3" ht="14.25" customHeight="1">
       <c r="C42" s="1"/>
     </row>
-    <row r="43" ht="14.25" customHeight="1">
+    <row r="43" spans="3:3" ht="14.25" customHeight="1">
       <c r="C43" s="1"/>
     </row>
-    <row r="44" ht="14.25" customHeight="1">
+    <row r="44" spans="3:3" ht="14.25" customHeight="1">
       <c r="C44" s="1"/>
     </row>
-    <row r="45" ht="14.25" customHeight="1">
+    <row r="45" spans="3:3" ht="14.25" customHeight="1">
       <c r="C45" s="1"/>
     </row>
-    <row r="46" ht="14.25" customHeight="1">
+    <row r="46" spans="3:3" ht="14.25" customHeight="1">
       <c r="C46" s="1"/>
     </row>
-    <row r="47" ht="14.25" customHeight="1">
+    <row r="47" spans="3:3" ht="14.25" customHeight="1">
       <c r="C47" s="1"/>
     </row>
-    <row r="48" ht="14.25" customHeight="1">
+    <row r="48" spans="3:3" ht="14.25" customHeight="1">
       <c r="C48" s="1"/>
     </row>
-    <row r="49" ht="14.25" customHeight="1">
+    <row r="49" spans="3:3" ht="14.25" customHeight="1">
       <c r="C49" s="1"/>
     </row>
-    <row r="50" ht="14.25" customHeight="1">
+    <row r="50" spans="3:3" ht="14.25" customHeight="1">
       <c r="C50" s="1"/>
     </row>
-    <row r="51" ht="14.25" customHeight="1">
+    <row r="51" spans="3:3" ht="14.25" customHeight="1">
       <c r="C51" s="1"/>
     </row>
-    <row r="52" ht="14.25" customHeight="1">
+    <row r="52" spans="3:3" ht="14.25" customHeight="1">
       <c r="C52" s="1"/>
     </row>
-    <row r="53" ht="14.25" customHeight="1">
+    <row r="53" spans="3:3" ht="14.25" customHeight="1">
       <c r="C53" s="1"/>
     </row>
-    <row r="54" ht="14.25" customHeight="1">
+    <row r="54" spans="3:3" ht="14.25" customHeight="1">
       <c r="C54" s="1"/>
     </row>
-    <row r="55" ht="14.25" customHeight="1">
+    <row r="55" spans="3:3" ht="14.25" customHeight="1">
       <c r="C55" s="1"/>
     </row>
-    <row r="56" ht="14.25" customHeight="1">
+    <row r="56" spans="3:3" ht="14.25" customHeight="1">
       <c r="C56" s="1"/>
     </row>
-    <row r="57" ht="14.25" customHeight="1">
+    <row r="57" spans="3:3" ht="14.25" customHeight="1">
       <c r="C57" s="1"/>
     </row>
-    <row r="58" ht="14.25" customHeight="1">
+    <row r="58" spans="3:3" ht="14.25" customHeight="1">
       <c r="C58" s="1"/>
     </row>
-    <row r="59" ht="14.25" customHeight="1">
+    <row r="59" spans="3:3" ht="14.25" customHeight="1">
       <c r="C59" s="1"/>
     </row>
-    <row r="60" ht="14.25" customHeight="1">
+    <row r="60" spans="3:3" ht="14.25" customHeight="1">
       <c r="C60" s="1"/>
     </row>
-    <row r="61" ht="14.25" customHeight="1">
+    <row r="61" spans="3:3" ht="14.25" customHeight="1">
       <c r="C61" s="1"/>
     </row>
-    <row r="62" ht="14.25" customHeight="1">
+    <row r="62" spans="3:3" ht="14.25" customHeight="1">
       <c r="C62" s="1"/>
     </row>
-    <row r="63" ht="14.25" customHeight="1">
+    <row r="63" spans="3:3" ht="14.25" customHeight="1">
       <c r="C63" s="1"/>
     </row>
-    <row r="64" ht="14.25" customHeight="1">
+    <row r="64" spans="3:3" ht="14.25" customHeight="1">
       <c r="C64" s="1"/>
     </row>
-    <row r="65" ht="14.25" customHeight="1">
+    <row r="65" spans="3:3" ht="14.25" customHeight="1">
       <c r="C65" s="1"/>
     </row>
-    <row r="66" ht="14.25" customHeight="1">
+    <row r="66" spans="3:3" ht="14.25" customHeight="1">
       <c r="C66" s="1"/>
     </row>
-    <row r="67" ht="14.25" customHeight="1">
+    <row r="67" spans="3:3" ht="14.25" customHeight="1">
       <c r="C67" s="1"/>
     </row>
-    <row r="68" ht="14.25" customHeight="1">
+    <row r="68" spans="3:3" ht="14.25" customHeight="1">
       <c r="C68" s="1"/>
     </row>
-    <row r="69" ht="14.25" customHeight="1">
+    <row r="69" spans="3:3" ht="14.25" customHeight="1">
       <c r="C69" s="1"/>
     </row>
-    <row r="70" ht="14.25" customHeight="1">
+    <row r="70" spans="3:3" ht="14.25" customHeight="1">
       <c r="C70" s="1"/>
     </row>
-    <row r="71" ht="14.25" customHeight="1">
+    <row r="71" spans="3:3" ht="14.25" customHeight="1">
       <c r="C71" s="1"/>
     </row>
-    <row r="72" ht="14.25" customHeight="1">
+    <row r="72" spans="3:3" ht="14.25" customHeight="1">
       <c r="C72" s="1"/>
     </row>
-    <row r="73" ht="14.25" customHeight="1">
+    <row r="73" spans="3:3" ht="14.25" customHeight="1">
       <c r="C73" s="1"/>
     </row>
-    <row r="74" ht="14.25" customHeight="1">
+    <row r="74" spans="3:3" ht="14.25" customHeight="1">
       <c r="C74" s="1"/>
     </row>
-    <row r="75" ht="14.25" customHeight="1">
+    <row r="75" spans="3:3" ht="14.25" customHeight="1">
       <c r="C75" s="1"/>
     </row>
-    <row r="76" ht="14.25" customHeight="1">
+    <row r="76" spans="3:3" ht="14.25" customHeight="1">
       <c r="C76" s="1"/>
     </row>
-    <row r="77" ht="14.25" customHeight="1">
+    <row r="77" spans="3:3" ht="14.25" customHeight="1">
       <c r="C77" s="1"/>
     </row>
-    <row r="78" ht="14.25" customHeight="1">
+    <row r="78" spans="3:3" ht="14.25" customHeight="1">
       <c r="C78" s="1"/>
     </row>
-    <row r="79" ht="14.25" customHeight="1">
+    <row r="79" spans="3:3" ht="14.25" customHeight="1">
       <c r="C79" s="1"/>
     </row>
-    <row r="80" ht="14.25" customHeight="1">
+    <row r="80" spans="3:3" ht="14.25" customHeight="1">
       <c r="C80" s="1"/>
     </row>
-    <row r="81" ht="14.25" customHeight="1">
+    <row r="81" spans="3:3" ht="14.25" customHeight="1">
       <c r="C81" s="1"/>
     </row>
-    <row r="82" ht="14.25" customHeight="1">
+    <row r="82" spans="3:3" ht="14.25" customHeight="1">
       <c r="C82" s="1"/>
     </row>
-    <row r="83" ht="14.25" customHeight="1">
+    <row r="83" spans="3:3" ht="14.25" customHeight="1">
       <c r="C83" s="1"/>
     </row>
-    <row r="84" ht="14.25" customHeight="1">
+    <row r="84" spans="3:3" ht="14.25" customHeight="1">
       <c r="C84" s="1"/>
     </row>
-    <row r="85" ht="14.25" customHeight="1">
+    <row r="85" spans="3:3" ht="14.25" customHeight="1">
       <c r="C85" s="1"/>
     </row>
-    <row r="86" ht="14.25" customHeight="1">
+    <row r="86" spans="3:3" ht="14.25" customHeight="1">
       <c r="C86" s="1"/>
     </row>
-    <row r="87" ht="14.25" customHeight="1">
+    <row r="87" spans="3:3" ht="14.25" customHeight="1">
       <c r="C87" s="1"/>
     </row>
-    <row r="88" ht="14.25" customHeight="1">
+    <row r="88" spans="3:3" ht="14.25" customHeight="1">
       <c r="C88" s="1"/>
     </row>
-    <row r="89" ht="14.25" customHeight="1">
+    <row r="89" spans="3:3" ht="14.25" customHeight="1">
       <c r="C89" s="1"/>
     </row>
-    <row r="90" ht="14.25" customHeight="1">
+    <row r="90" spans="3:3" ht="14.25" customHeight="1">
       <c r="C90" s="1"/>
     </row>
-    <row r="91" ht="14.25" customHeight="1">
+    <row r="91" spans="3:3" ht="14.25" customHeight="1">
       <c r="C91" s="1"/>
     </row>
-    <row r="92" ht="14.25" customHeight="1">
+    <row r="92" spans="3:3" ht="14.25" customHeight="1">
       <c r="C92" s="1"/>
     </row>
-    <row r="93" ht="14.25" customHeight="1">
+    <row r="93" spans="3:3" ht="14.25" customHeight="1">
       <c r="C93" s="1"/>
     </row>
-    <row r="94" ht="14.25" customHeight="1">
+    <row r="94" spans="3:3" ht="14.25" customHeight="1">
       <c r="C94" s="1"/>
     </row>
-    <row r="95" ht="14.25" customHeight="1">
+    <row r="95" spans="3:3" ht="14.25" customHeight="1">
       <c r="C95" s="1"/>
     </row>
-    <row r="96" ht="14.25" customHeight="1">
+    <row r="96" spans="3:3" ht="14.25" customHeight="1">
       <c r="C96" s="1"/>
     </row>
-    <row r="97" ht="14.25" customHeight="1">
+    <row r="97" spans="3:3" ht="14.25" customHeight="1">
       <c r="C97" s="1"/>
     </row>
-    <row r="98" ht="14.25" customHeight="1">
+    <row r="98" spans="3:3" ht="14.25" customHeight="1">
       <c r="C98" s="1"/>
     </row>
-    <row r="99" ht="14.25" customHeight="1">
+    <row r="99" spans="3:3" ht="14.25" customHeight="1">
       <c r="C99" s="1"/>
     </row>
-    <row r="100" ht="14.25" customHeight="1">
+    <row r="100" spans="3:3" ht="14.25" customHeight="1">
       <c r="C100" s="1"/>
     </row>
-    <row r="101" ht="14.25" customHeight="1">
+    <row r="101" spans="3:3" ht="14.25" customHeight="1">
       <c r="C101" s="1"/>
     </row>
-    <row r="102" ht="14.25" customHeight="1">
+    <row r="102" spans="3:3" ht="14.25" customHeight="1">
       <c r="C102" s="1"/>
     </row>
-    <row r="103" ht="14.25" customHeight="1">
+    <row r="103" spans="3:3" ht="14.25" customHeight="1">
       <c r="C103" s="1"/>
     </row>
-    <row r="104" ht="14.25" customHeight="1">
+    <row r="104" spans="3:3" ht="14.25" customHeight="1">
       <c r="C104" s="1"/>
     </row>
-    <row r="105" ht="14.25" customHeight="1">
+    <row r="105" spans="3:3" ht="14.25" customHeight="1">
       <c r="C105" s="1"/>
     </row>
-    <row r="106" ht="14.25" customHeight="1">
+    <row r="106" spans="3:3" ht="14.25" customHeight="1">
       <c r="C106" s="1"/>
     </row>
-    <row r="107" ht="14.25" customHeight="1">
+    <row r="107" spans="3:3" ht="14.25" customHeight="1">
       <c r="C107" s="1"/>
     </row>
-    <row r="108" ht="14.25" customHeight="1">
+    <row r="108" spans="3:3" ht="14.25" customHeight="1">
       <c r="C108" s="1"/>
     </row>
-    <row r="109" ht="14.25" customHeight="1">
+    <row r="109" spans="3:3" ht="14.25" customHeight="1">
       <c r="C109" s="1"/>
     </row>
-    <row r="110" ht="14.25" customHeight="1">
+    <row r="110" spans="3:3" ht="14.25" customHeight="1">
       <c r="C110" s="1"/>
     </row>
-    <row r="111" ht="14.25" customHeight="1">
+    <row r="111" spans="3:3" ht="14.25" customHeight="1">
       <c r="C111" s="1"/>
     </row>
-    <row r="112" ht="14.25" customHeight="1">
+    <row r="112" spans="3:3" ht="14.25" customHeight="1">
       <c r="C112" s="1"/>
     </row>
-    <row r="113" ht="14.25" customHeight="1">
+    <row r="113" spans="3:3" ht="14.25" customHeight="1">
       <c r="C113" s="1"/>
     </row>
-    <row r="114" ht="14.25" customHeight="1">
+    <row r="114" spans="3:3" ht="14.25" customHeight="1">
       <c r="C114" s="1"/>
     </row>
-    <row r="115" ht="14.25" customHeight="1">
+    <row r="115" spans="3:3" ht="14.25" customHeight="1">
       <c r="C115" s="1"/>
     </row>
-    <row r="116" ht="14.25" customHeight="1">
+    <row r="116" spans="3:3" ht="14.25" customHeight="1">
       <c r="C116" s="1"/>
     </row>
-    <row r="117" ht="14.25" customHeight="1">
+    <row r="117" spans="3:3" ht="14.25" customHeight="1">
       <c r="C117" s="1"/>
     </row>
-    <row r="118" ht="14.25" customHeight="1">
+    <row r="118" spans="3:3" ht="14.25" customHeight="1">
       <c r="C118" s="1"/>
     </row>
-    <row r="119" ht="14.25" customHeight="1">
+    <row r="119" spans="3:3" ht="14.25" customHeight="1">
       <c r="C119" s="1"/>
     </row>
-    <row r="120" ht="14.25" customHeight="1">
+    <row r="120" spans="3:3" ht="14.25" customHeight="1">
       <c r="C120" s="1"/>
     </row>
-    <row r="121" ht="14.25" customHeight="1">
+    <row r="121" spans="3:3" ht="14.25" customHeight="1">
       <c r="C121" s="1"/>
     </row>
-    <row r="122" ht="14.25" customHeight="1">
+    <row r="122" spans="3:3" ht="14.25" customHeight="1">
       <c r="C122" s="1"/>
     </row>
-    <row r="123" ht="14.25" customHeight="1">
+    <row r="123" spans="3:3" ht="14.25" customHeight="1">
       <c r="C123" s="1"/>
     </row>
-    <row r="124" ht="14.25" customHeight="1">
+    <row r="124" spans="3:3" ht="14.25" customHeight="1">
       <c r="C124" s="1"/>
     </row>
-    <row r="125" ht="14.25" customHeight="1">
+    <row r="125" spans="3:3" ht="14.25" customHeight="1">
       <c r="C125" s="1"/>
     </row>
-    <row r="126" ht="14.25" customHeight="1">
+    <row r="126" spans="3:3" ht="14.25" customHeight="1">
       <c r="C126" s="1"/>
     </row>
-    <row r="127" ht="14.25" customHeight="1">
+    <row r="127" spans="3:3" ht="14.25" customHeight="1">
       <c r="C127" s="1"/>
     </row>
-    <row r="128" ht="14.25" customHeight="1">
+    <row r="128" spans="3:3" ht="14.25" customHeight="1">
       <c r="C128" s="1"/>
     </row>
-    <row r="129" ht="14.25" customHeight="1">
+    <row r="129" spans="3:3" ht="14.25" customHeight="1">
       <c r="C129" s="1"/>
     </row>
-    <row r="130" ht="14.25" customHeight="1">
+    <row r="130" spans="3:3" ht="14.25" customHeight="1">
       <c r="C130" s="1"/>
     </row>
-    <row r="131" ht="14.25" customHeight="1">
+    <row r="131" spans="3:3" ht="14.25" customHeight="1">
       <c r="C131" s="1"/>
     </row>
-    <row r="132" ht="14.25" customHeight="1">
+    <row r="132" spans="3:3" ht="14.25" customHeight="1">
       <c r="C132" s="1"/>
     </row>
-    <row r="133" ht="14.25" customHeight="1">
+    <row r="133" spans="3:3" ht="14.25" customHeight="1">
       <c r="C133" s="1"/>
     </row>
-    <row r="134" ht="14.25" customHeight="1">
+    <row r="134" spans="3:3" ht="14.25" customHeight="1">
       <c r="C134" s="1"/>
     </row>
-    <row r="135" ht="14.25" customHeight="1">
+    <row r="135" spans="3:3" ht="14.25" customHeight="1">
       <c r="C135" s="1"/>
     </row>
-    <row r="136" ht="14.25" customHeight="1">
+    <row r="136" spans="3:3" ht="14.25" customHeight="1">
       <c r="C136" s="1"/>
     </row>
-    <row r="137" ht="14.25" customHeight="1">
+    <row r="137" spans="3:3" ht="14.25" customHeight="1">
       <c r="C137" s="1"/>
     </row>
-    <row r="138" ht="14.25" customHeight="1">
+    <row r="138" spans="3:3" ht="14.25" customHeight="1">
       <c r="C138" s="1"/>
     </row>
-    <row r="139" ht="14.25" customHeight="1">
+    <row r="139" spans="3:3" ht="14.25" customHeight="1">
       <c r="C139" s="1"/>
     </row>
-    <row r="140" ht="14.25" customHeight="1">
+    <row r="140" spans="3:3" ht="14.25" customHeight="1">
       <c r="C140" s="1"/>
     </row>
-    <row r="141" ht="14.25" customHeight="1">
+    <row r="141" spans="3:3" ht="14.25" customHeight="1">
       <c r="C141" s="1"/>
     </row>
-    <row r="142" ht="14.25" customHeight="1">
+    <row r="142" spans="3:3" ht="14.25" customHeight="1">
       <c r="C142" s="1"/>
     </row>
-    <row r="143" ht="14.25" customHeight="1">
+    <row r="143" spans="3:3" ht="14.25" customHeight="1">
       <c r="C143" s="1"/>
     </row>
-    <row r="144" ht="14.25" customHeight="1">
+    <row r="144" spans="3:3" ht="14.25" customHeight="1">
       <c r="C144" s="1"/>
     </row>
-    <row r="145" ht="14.25" customHeight="1">
+    <row r="145" spans="3:3" ht="14.25" customHeight="1">
       <c r="C145" s="1"/>
     </row>
-    <row r="146" ht="14.25" customHeight="1">
+    <row r="146" spans="3:3" ht="14.25" customHeight="1">
       <c r="C146" s="1"/>
     </row>
-    <row r="147" ht="14.25" customHeight="1">
+    <row r="147" spans="3:3" ht="14.25" customHeight="1">
       <c r="C147" s="1"/>
     </row>
-    <row r="148" ht="14.25" customHeight="1">
+    <row r="148" spans="3:3" ht="14.25" customHeight="1">
       <c r="C148" s="1"/>
     </row>
-    <row r="149" ht="14.25" customHeight="1">
+    <row r="149" spans="3:3" ht="14.25" customHeight="1">
       <c r="C149" s="1"/>
     </row>
-    <row r="150" ht="14.25" customHeight="1">
+    <row r="150" spans="3:3" ht="14.25" customHeight="1">
       <c r="C150" s="1"/>
     </row>
-    <row r="151" ht="14.25" customHeight="1">
+    <row r="151" spans="3:3" ht="14.25" customHeight="1">
       <c r="C151" s="1"/>
     </row>
-    <row r="152" ht="14.25" customHeight="1">
+    <row r="152" spans="3:3" ht="14.25" customHeight="1">
       <c r="C152" s="1"/>
     </row>
-    <row r="153" ht="14.25" customHeight="1">
+    <row r="153" spans="3:3" ht="14.25" customHeight="1">
       <c r="C153" s="1"/>
     </row>
-    <row r="154" ht="14.25" customHeight="1">
+    <row r="154" spans="3:3" ht="14.25" customHeight="1">
       <c r="C154" s="1"/>
     </row>
-    <row r="155" ht="14.25" customHeight="1">
+    <row r="155" spans="3:3" ht="14.25" customHeight="1">
       <c r="C155" s="1"/>
     </row>
-    <row r="156" ht="14.25" customHeight="1">
+    <row r="156" spans="3:3" ht="14.25" customHeight="1">
       <c r="C156" s="1"/>
     </row>
-    <row r="157" ht="14.25" customHeight="1">
+    <row r="157" spans="3:3" ht="14.25" customHeight="1">
       <c r="C157" s="1"/>
     </row>
-    <row r="158" ht="14.25" customHeight="1">
+    <row r="158" spans="3:3" ht="14.25" customHeight="1">
       <c r="C158" s="1"/>
     </row>
-    <row r="159" ht="14.25" customHeight="1">
+    <row r="159" spans="3:3" ht="14.25" customHeight="1">
       <c r="C159" s="1"/>
     </row>
-    <row r="160" ht="14.25" customHeight="1">
+    <row r="160" spans="3:3" ht="14.25" customHeight="1">
       <c r="C160" s="1"/>
     </row>
-    <row r="161" ht="14.25" customHeight="1">
+    <row r="161" spans="3:3" ht="14.25" customHeight="1">
       <c r="C161" s="1"/>
     </row>
-    <row r="162" ht="14.25" customHeight="1">
+    <row r="162" spans="3:3" ht="14.25" customHeight="1">
       <c r="C162" s="1"/>
     </row>
-    <row r="163" ht="14.25" customHeight="1">
+    <row r="163" spans="3:3" ht="14.25" customHeight="1">
       <c r="C163" s="1"/>
     </row>
-    <row r="164" ht="14.25" customHeight="1">
+    <row r="164" spans="3:3" ht="14.25" customHeight="1">
       <c r="C164" s="1"/>
     </row>
-    <row r="165" ht="14.25" customHeight="1">
+    <row r="165" spans="3:3" ht="14.25" customHeight="1">
       <c r="C165" s="1"/>
     </row>
-    <row r="166" ht="14.25" customHeight="1">
+    <row r="166" spans="3:3" ht="14.25" customHeight="1">
       <c r="C166" s="1"/>
     </row>
-    <row r="167" ht="14.25" customHeight="1">
+    <row r="167" spans="3:3" ht="14.25" customHeight="1">
       <c r="C167" s="1"/>
     </row>
-    <row r="168" ht="14.25" customHeight="1">
+    <row r="168" spans="3:3" ht="14.25" customHeight="1">
       <c r="C168" s="1"/>
     </row>
-    <row r="169" ht="14.25" customHeight="1">
+    <row r="169" spans="3:3" ht="14.25" customHeight="1">
       <c r="C169" s="1"/>
     </row>
-    <row r="170" ht="14.25" customHeight="1">
+    <row r="170" spans="3:3" ht="14.25" customHeight="1">
       <c r="C170" s="1"/>
     </row>
-    <row r="171" ht="14.25" customHeight="1">
+    <row r="171" spans="3:3" ht="14.25" customHeight="1">
       <c r="C171" s="1"/>
     </row>
-    <row r="172" ht="14.25" customHeight="1">
+    <row r="172" spans="3:3" ht="14.25" customHeight="1">
       <c r="C172" s="1"/>
     </row>
-    <row r="173" ht="14.25" customHeight="1">
+    <row r="173" spans="3:3" ht="14.25" customHeight="1">
       <c r="C173" s="1"/>
     </row>
-    <row r="174" ht="14.25" customHeight="1">
+    <row r="174" spans="3:3" ht="14.25" customHeight="1">
       <c r="C174" s="1"/>
     </row>
-    <row r="175" ht="14.25" customHeight="1">
+    <row r="175" spans="3:3" ht="14.25" customHeight="1">
       <c r="C175" s="1"/>
     </row>
-    <row r="176" ht="14.25" customHeight="1">
+    <row r="176" spans="3:3" ht="14.25" customHeight="1">
       <c r="C176" s="1"/>
     </row>
-    <row r="177" ht="14.25" customHeight="1">
+    <row r="177" spans="3:3" ht="14.25" customHeight="1">
       <c r="C177" s="1"/>
     </row>
-    <row r="178" ht="14.25" customHeight="1">
+    <row r="178" spans="3:3" ht="14.25" customHeight="1">
       <c r="C178" s="1"/>
     </row>
-    <row r="179" ht="14.25" customHeight="1">
+    <row r="179" spans="3:3" ht="14.25" customHeight="1">
       <c r="C179" s="1"/>
     </row>
-    <row r="180" ht="14.25" customHeight="1">
+    <row r="180" spans="3:3" ht="14.25" customHeight="1">
       <c r="C180" s="1"/>
     </row>
-    <row r="181" ht="14.25" customHeight="1">
+    <row r="181" spans="3:3" ht="14.25" customHeight="1">
       <c r="C181" s="1"/>
     </row>
-    <row r="182" ht="14.25" customHeight="1">
+    <row r="182" spans="3:3" ht="14.25" customHeight="1">
       <c r="C182" s="1"/>
     </row>
-    <row r="183" ht="14.25" customHeight="1">
+    <row r="183" spans="3:3" ht="14.25" customHeight="1">
       <c r="C183" s="1"/>
     </row>
-    <row r="184" ht="14.25" customHeight="1">
+    <row r="184" spans="3:3" ht="14.25" customHeight="1">
       <c r="C184" s="1"/>
     </row>
-    <row r="185" ht="14.25" customHeight="1">
+    <row r="185" spans="3:3" ht="14.25" customHeight="1">
       <c r="C185" s="1"/>
     </row>
-    <row r="186" ht="14.25" customHeight="1">
+    <row r="186" spans="3:3" ht="14.25" customHeight="1">
       <c r="C186" s="1"/>
     </row>
-    <row r="187" ht="14.25" customHeight="1">
+    <row r="187" spans="3:3" ht="14.25" customHeight="1">
       <c r="C187" s="1"/>
     </row>
-    <row r="188" ht="14.25" customHeight="1">
+    <row r="188" spans="3:3" ht="14.25" customHeight="1">
       <c r="C188" s="1"/>
     </row>
-    <row r="189" ht="14.25" customHeight="1">
+    <row r="189" spans="3:3" ht="14.25" customHeight="1">
       <c r="C189" s="1"/>
     </row>
-    <row r="190" ht="14.25" customHeight="1">
+    <row r="190" spans="3:3" ht="14.25" customHeight="1">
       <c r="C190" s="1"/>
     </row>
-    <row r="191" ht="14.25" customHeight="1">
+    <row r="191" spans="3:3" ht="14.25" customHeight="1">
       <c r="C191" s="1"/>
     </row>
-    <row r="192" ht="14.25" customHeight="1">
+    <row r="192" spans="3:3" ht="14.25" customHeight="1">
       <c r="C192" s="1"/>
     </row>
-    <row r="193" ht="14.25" customHeight="1">
+    <row r="193" spans="3:3" ht="14.25" customHeight="1">
       <c r="C193" s="1"/>
     </row>
-    <row r="194" ht="14.25" customHeight="1">
+    <row r="194" spans="3:3" ht="14.25" customHeight="1">
       <c r="C194" s="1"/>
     </row>
-    <row r="195" ht="14.25" customHeight="1">
+    <row r="195" spans="3:3" ht="14.25" customHeight="1">
       <c r="C195" s="1"/>
     </row>
-    <row r="196" ht="14.25" customHeight="1">
+    <row r="196" spans="3:3" ht="14.25" customHeight="1">
       <c r="C196" s="1"/>
     </row>
-    <row r="197" ht="14.25" customHeight="1">
+    <row r="197" spans="3:3" ht="14.25" customHeight="1">
       <c r="C197" s="1"/>
     </row>
-    <row r="198" ht="14.25" customHeight="1">
+    <row r="198" spans="3:3" ht="14.25" customHeight="1">
       <c r="C198" s="1"/>
     </row>
-    <row r="199" ht="14.25" customHeight="1">
+    <row r="199" spans="3:3" ht="14.25" customHeight="1">
       <c r="C199" s="1"/>
     </row>
-    <row r="200" ht="14.25" customHeight="1">
+    <row r="200" spans="3:3" ht="14.25" customHeight="1">
       <c r="C200" s="1"/>
     </row>
-    <row r="201" ht="14.25" customHeight="1">
+    <row r="201" spans="3:3" ht="14.25" customHeight="1">
       <c r="C201" s="1"/>
     </row>
-    <row r="202" ht="14.25" customHeight="1">
+    <row r="202" spans="3:3" ht="14.25" customHeight="1">
       <c r="C202" s="1"/>
     </row>
-    <row r="203" ht="14.25" customHeight="1">
+    <row r="203" spans="3:3" ht="14.25" customHeight="1">
       <c r="C203" s="1"/>
     </row>
-    <row r="204" ht="14.25" customHeight="1">
+    <row r="204" spans="3:3" ht="14.25" customHeight="1">
       <c r="C204" s="1"/>
     </row>
-    <row r="205" ht="14.25" customHeight="1">
+    <row r="205" spans="3:3" ht="14.25" customHeight="1">
       <c r="C205" s="1"/>
     </row>
-    <row r="206" ht="14.25" customHeight="1">
+    <row r="206" spans="3:3" ht="14.25" customHeight="1">
       <c r="C206" s="1"/>
     </row>
-    <row r="207" ht="14.25" customHeight="1">
+    <row r="207" spans="3:3" ht="14.25" customHeight="1">
       <c r="C207" s="1"/>
     </row>
-    <row r="208" ht="14.25" customHeight="1">
+    <row r="208" spans="3:3" ht="14.25" customHeight="1">
       <c r="C208" s="1"/>
     </row>
-    <row r="209" ht="14.25" customHeight="1">
+    <row r="209" spans="3:3" ht="14.25" customHeight="1">
       <c r="C209" s="1"/>
     </row>
-    <row r="210" ht="14.25" customHeight="1">
+    <row r="210" spans="3:3" ht="14.25" customHeight="1">
       <c r="C210" s="1"/>
     </row>
-    <row r="211" ht="14.25" customHeight="1">
+    <row r="211" spans="3:3" ht="14.25" customHeight="1">
       <c r="C211" s="1"/>
     </row>
-    <row r="212" ht="14.25" customHeight="1">
+    <row r="212" spans="3:3" ht="14.25" customHeight="1">
       <c r="C212" s="1"/>
     </row>
-    <row r="213" ht="14.25" customHeight="1">
+    <row r="213" spans="3:3" ht="14.25" customHeight="1">
       <c r="C213" s="1"/>
     </row>
-    <row r="214" ht="14.25" customHeight="1">
+    <row r="214" spans="3:3" ht="14.25" customHeight="1">
       <c r="C214" s="1"/>
     </row>
-    <row r="215" ht="14.25" customHeight="1">
+    <row r="215" spans="3:3" ht="14.25" customHeight="1">
       <c r="C215" s="1"/>
     </row>
-    <row r="216" ht="14.25" customHeight="1">
+    <row r="216" spans="3:3" ht="14.25" customHeight="1">
       <c r="C216" s="1"/>
     </row>
-    <row r="217" ht="14.25" customHeight="1">
+    <row r="217" spans="3:3" ht="14.25" customHeight="1">
       <c r="C217" s="1"/>
     </row>
-    <row r="218" ht="14.25" customHeight="1">
+    <row r="218" spans="3:3" ht="14.25" customHeight="1">
       <c r="C218" s="1"/>
     </row>
-    <row r="219" ht="14.25" customHeight="1">
+    <row r="219" spans="3:3" ht="14.25" customHeight="1">
       <c r="C219" s="1"/>
     </row>
-    <row r="220" ht="14.25" customHeight="1">
+    <row r="220" spans="3:3" ht="14.25" customHeight="1">
       <c r="C220" s="1"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="221" spans="3:3" ht="15.75" customHeight="1"/>
+    <row r="222" spans="3:3" ht="15.75" customHeight="1"/>
+    <row r="223" spans="3:3" ht="15.75" customHeight="1"/>
+    <row r="224" spans="3:3" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
@@ -3925,18 +4969,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="G7:G8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="C3:K4"/>
-    <mergeCell ref="E5:K5"/>
-    <mergeCell ref="F6:K6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:E8"/>
-    <mergeCell ref="F7:F8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
     <mergeCell ref="C19:D19"/>
@@ -3947,482 +4979,509 @@
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="C14:D14"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:E8"/>
+    <mergeCell ref="F7:F8"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G7:G8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="C3:K4"/>
+    <mergeCell ref="E5:K5"/>
+    <mergeCell ref="F6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
-  <pageMargins bottom="0.7480314960629921" footer="0.0" header="0.0" left="0.47" right="0.7086614173228347" top="0.7480314960629921"/>
+  <pageMargins left="0.47" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="56" orientation="landscape"/>
   <headerFooter>
     <oddFooter>&amp;LElaborado por: Ing Jenny A Ruiz R, Mónica  Gómez Docentes TC del Departamento de Ciencias de la  Computación IREB PROYECTO DE CHECK LIST  (CASO DE ESTUDIO ACADÉMICO)&amp;C&amp;P de &amp;R&amp;D</oddFooter>
   </headerFooter>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="36.43"/>
-    <col customWidth="1" min="3" max="3" width="16.14"/>
-    <col customWidth="1" min="4" max="24" width="10.71"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="36.453125" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="4" max="24" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="29"/>
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="1:26" ht="51" customHeight="1">
+      <c r="A1" s="13"/>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+    </row>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1">
+      <c r="B2" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="B2" s="32" t="s">
+      <c r="C2" s="53">
+        <v>46126</v>
+      </c>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1">
+      <c r="B3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="33">
-        <v>46126.0</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="32" t="s">
+      <c r="C3" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="34" t="s">
+      <c r="D3" s="38"/>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="B4" s="15" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="32" t="s">
+      <c r="C4" s="54" t="s">
         <v>59</v>
       </c>
-      <c r="C4" s="34" t="s">
+      <c r="D4" s="38"/>
+    </row>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A6" s="50" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="30.75" customHeight="1">
-      <c r="A6" s="35" t="s">
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+    </row>
+    <row r="7" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A7" s="16" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="36" t="s">
+      <c r="B7" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="C7" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="D7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="38" t="s">
+    </row>
+    <row r="8" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A8" s="19">
+        <v>1</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="C8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A9" s="19">
+        <v>2</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="42"/>
-    </row>
-    <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="40" t="s">
+      <c r="C9" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A10" s="19">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="43" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="44"/>
-    </row>
-    <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="C10" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="11" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A11" s="19">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="42"/>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="C11" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="22"/>
+    </row>
+    <row r="12" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A12" s="19">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="42"/>
-    </row>
-    <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="C12" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="22"/>
+    </row>
+    <row r="13" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A13" s="19">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="42"/>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="B13" s="40" t="s">
+      <c r="C13" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="22"/>
+    </row>
+    <row r="14" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A14" s="19">
+        <v>7</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="42"/>
-    </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="B14" s="40" t="s">
+      <c r="C14" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" spans="1:26" ht="43.5">
+      <c r="A15" s="19">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="42"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="39">
-        <v>8.0</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="C15" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" spans="1:26" ht="58">
+      <c r="A16" s="23">
+        <v>9</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="42"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="45">
-        <v>9.0</v>
-      </c>
-      <c r="B16" s="46" t="s">
+      <c r="C16" s="25"/>
+      <c r="D16" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A17" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" ht="20.25" customHeight="1">
-      <c r="A17" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="22">
+      <c r="B17" s="38"/>
+      <c r="C17" s="8">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$8:$C$16)</f>
         <v>8</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="8">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$D$8:$D$16)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="48" t="s">
+    <row r="18" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A18" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="27">
+        <f t="shared" ref="C18:D18" si="0">C17/9</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="D18" s="27">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A20" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="49">
-        <f t="shared" ref="C18:D18" si="1">C17/9</f>
-        <v>0.8888888889</v>
-      </c>
-      <c r="D18" s="49">
-        <f t="shared" si="1"/>
-        <v>0.1111111111</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="22"/>
-    </row>
-    <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+    </row>
+    <row r="21" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A21" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="32.25" customHeight="1">
+      <c r="A22" s="19">
+        <v>1</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-    </row>
-    <row r="21" ht="20.25" customHeight="1">
-      <c r="A21" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" ht="32.25" customHeight="1">
-      <c r="A22" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="40" t="s">
+      <c r="C22" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="22"/>
+    </row>
+    <row r="23" spans="1:4" ht="29">
+      <c r="A23" s="19">
+        <v>2</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="42"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="40" t="s">
+      <c r="C23" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="22"/>
+    </row>
+    <row r="24" spans="1:4" ht="29">
+      <c r="A24" s="19">
+        <v>3</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="42"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="40" t="s">
+      <c r="C24" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="22"/>
+    </row>
+    <row r="25" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A25" s="19">
+        <v>4</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="42"/>
-    </row>
-    <row r="25" ht="34.5" customHeight="1">
-      <c r="A25" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="40" t="s">
+      <c r="C25" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="22"/>
+    </row>
+    <row r="26" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A26" s="23">
+        <v>5</v>
+      </c>
+      <c r="B26" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="42"/>
-    </row>
-    <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="56"/>
-    </row>
-    <row r="27" ht="24.75" customHeight="1">
-      <c r="A27" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="22">
+      <c r="C26" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="32"/>
+    </row>
+    <row r="27" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A27" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="8">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$22:$C$26)</f>
         <v>5</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="8">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$D$22:$D$26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="28.5" customHeight="1">
-      <c r="A28" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="49">
-        <f t="shared" ref="C28:D28" si="2">C27/5</f>
+    <row r="28" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A28" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="38"/>
+      <c r="C28" s="27">
+        <f t="shared" ref="C28:D28" si="1">C27/5</f>
         <v>1</v>
       </c>
-      <c r="D28" s="49">
-        <f t="shared" si="2"/>
+      <c r="D28" s="27">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="48"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="22"/>
-    </row>
-    <row r="30" ht="24.0" customHeight="1">
-      <c r="A30" s="35" t="s">
+    <row r="29" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="24" customHeight="1">
+      <c r="A30" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+    </row>
+    <row r="31" spans="1:4" ht="24" customHeight="1">
+      <c r="A31" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A32" s="19">
+        <v>1</v>
+      </c>
+      <c r="B32" s="20" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="31" ht="24.0" customHeight="1">
-      <c r="A31" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" ht="37.5" customHeight="1">
-      <c r="A32" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B32" s="40" t="s">
+      <c r="C32" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="25"/>
+    </row>
+    <row r="33" spans="1:4" ht="48" customHeight="1">
+      <c r="A33" s="19">
+        <v>2</v>
+      </c>
+      <c r="B33" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="47"/>
-    </row>
-    <row r="33" ht="37.5" customHeight="1">
-      <c r="A33" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B33" s="40" t="s">
+      <c r="C33" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="25"/>
+    </row>
+    <row r="34" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A34" s="23">
+        <v>3</v>
+      </c>
+      <c r="B34" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="47"/>
-    </row>
-    <row r="34" ht="37.5" customHeight="1">
-      <c r="A34" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="B34" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="57" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" ht="24.0" customHeight="1">
-      <c r="A35" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="22">
+      <c r="C34" s="25"/>
+      <c r="D34" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="24" customHeight="1">
+      <c r="A35" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="38"/>
+      <c r="C35" s="8">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$C$32:$C$34)</f>
         <v>2</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="8">
         <f>COUNTA('MODELO LISTA DE COMPROBACION - '!$D$32:$D$34)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="24.0" customHeight="1">
-      <c r="A36" s="48" t="s">
+    <row r="36" spans="1:4" ht="24" customHeight="1">
+      <c r="A36" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="38"/>
+      <c r="C36" s="27">
+        <f t="shared" ref="C36:D36" si="2">C35/3</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D36" s="27">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="38" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="39" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A40" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+    </row>
+    <row r="41" spans="1:4" ht="30" customHeight="1">
+      <c r="B41" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="30" customHeight="1">
+      <c r="B42" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="49">
-        <f t="shared" ref="C36:D36" si="3">C35/3</f>
-        <v>0.6666666667</v>
-      </c>
-      <c r="D36" s="49">
-        <f t="shared" si="3"/>
-        <v>0.3333333333</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="58" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="22">
-        <v>89.0</v>
-      </c>
-    </row>
-    <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="59">
-        <v>67.0</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="C44" s="22"/>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="C45" s="22"/>
-    </row>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+      <c r="C42" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="30" customHeight="1">
+      <c r="B43" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="14.25" customHeight="1">
+      <c r="C44" s="8"/>
+    </row>
+    <row r="45" spans="1:4" ht="14.25" customHeight="1">
+      <c r="C45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -5377,11 +6436,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="C1:D1"/>
@@ -5391,525 +6445,545 @@
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <conditionalFormatting sqref="A32:D34">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(A32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="22" priority="2" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="21" priority="3" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="20" priority="4" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="19" priority="5" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:D26">
-    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="18" priority="6" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:D26">
-    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="17" priority="7" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:D34">
-    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="16" priority="8" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="3">
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="36.43"/>
-    <col customWidth="1" min="3" max="3" width="16.14"/>
-    <col customWidth="1" min="4" max="4" width="21.57"/>
-    <col customWidth="1" min="5" max="24" width="10.71"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="36.453125" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="4" max="4" width="21.54296875" customWidth="1"/>
+    <col min="5" max="24" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="29"/>
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="1:26" ht="51" customHeight="1">
+      <c r="A1" s="13"/>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+    </row>
+    <row r="2" spans="1:26" ht="14.25" customHeight="1">
+      <c r="B2" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-    </row>
-    <row r="2" ht="14.25" customHeight="1">
-      <c r="B2" s="32" t="s">
+      <c r="C2" s="53">
+        <v>46126</v>
+      </c>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1">
+      <c r="B3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="33">
-        <v>46126.0</v>
-      </c>
-    </row>
-    <row r="3" ht="14.25" customHeight="1">
-      <c r="B3" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="34" t="s">
+      <c r="C3" s="54" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="38"/>
+    </row>
+    <row r="4" spans="1:26" ht="14.25" customHeight="1">
+      <c r="B4" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1">
-      <c r="B4" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="30.75" customHeight="1">
-      <c r="A6" s="35" t="s">
+      <c r="D4" s="38"/>
+    </row>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A6" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+    </row>
+    <row r="7" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A7" s="16" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="36" t="s">
+      <c r="B7" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="C7" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="D7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="38" t="s">
+    </row>
+    <row r="8" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A8" s="19">
+        <v>1</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="C8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A9" s="19">
+        <v>2</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="42"/>
-    </row>
-    <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="40" t="s">
+      <c r="C9" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A10" s="19">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="42"/>
-    </row>
-    <row r="10" ht="30.75" customHeight="1">
-      <c r="A10" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A11" s="19">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="C11" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="22"/>
+    </row>
+    <row r="12" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A12" s="19">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="42"/>
-    </row>
-    <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="C12" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="22"/>
+    </row>
+    <row r="13" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A13" s="19">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="42"/>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="B13" s="40" t="s">
+      <c r="C13" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="22"/>
+    </row>
+    <row r="14" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A14" s="19">
+        <v>7</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="42"/>
-    </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="B14" s="40" t="s">
+      <c r="C14" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" spans="1:26" ht="44.25" customHeight="1">
+      <c r="A15" s="19">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="42"/>
-    </row>
-    <row r="15" ht="44.25" customHeight="1">
-      <c r="A15" s="39">
-        <v>8.0</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="C15" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" spans="1:26" ht="64.5" customHeight="1">
+      <c r="A16" s="23">
+        <v>9</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="42"/>
-    </row>
-    <row r="16" ht="64.5" customHeight="1">
-      <c r="A16" s="45">
-        <v>9.0</v>
-      </c>
-      <c r="B16" s="46" t="s">
+      <c r="C16" s="25"/>
+      <c r="D16" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A17" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" ht="20.25" customHeight="1">
-      <c r="A17" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="22">
+      <c r="B17" s="38"/>
+      <c r="C17" s="8">
         <f>COUNTA('Hoja 1'!$C$8:$C$16)</f>
         <v>7</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="8">
         <f>COUNTA('Hoja 1'!$D$8:$D$16)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="48" t="s">
+    <row r="18" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A18" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="27">
+        <f t="shared" ref="C18:D18" si="0">C17/9</f>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="D18" s="27">
+        <f t="shared" si="0"/>
+        <v>0.22222222222222221</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A20" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="49">
-        <f t="shared" ref="C18:D18" si="1">C17/9</f>
-        <v>0.7777777778</v>
-      </c>
-      <c r="D18" s="49">
-        <f t="shared" si="1"/>
-        <v>0.2222222222</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="22"/>
-    </row>
-    <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+    </row>
+    <row r="21" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A21" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="32.25" customHeight="1">
+      <c r="A22" s="19">
+        <v>1</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-    </row>
-    <row r="21" ht="20.25" customHeight="1">
-      <c r="A21" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" ht="32.25" customHeight="1">
-      <c r="A22" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="40" t="s">
+      <c r="C22" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="22"/>
+    </row>
+    <row r="23" spans="1:4" ht="29">
+      <c r="A23" s="19">
+        <v>2</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="42"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="40" t="s">
+      <c r="C23" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="22"/>
+    </row>
+    <row r="24" spans="1:4" ht="29">
+      <c r="A24" s="19">
+        <v>3</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="42"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="40" t="s">
+      <c r="C24" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="22"/>
+    </row>
+    <row r="25" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A25" s="19">
+        <v>4</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="42"/>
-    </row>
-    <row r="25" ht="34.5" customHeight="1">
-      <c r="A25" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="40" t="s">
+      <c r="C25" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="22"/>
+    </row>
+    <row r="26" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A26" s="23">
+        <v>5</v>
+      </c>
+      <c r="B26" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="42"/>
-    </row>
-    <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="56"/>
-    </row>
-    <row r="27" ht="24.75" customHeight="1">
-      <c r="A27" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="22">
+      <c r="C26" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="32"/>
+    </row>
+    <row r="27" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A27" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="8">
         <f>COUNTA('Hoja 1'!$C$22:$C$26)</f>
         <v>5</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="8">
         <f>COUNTA('Hoja 1'!$D$22:$D$26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="28.5" customHeight="1">
-      <c r="A28" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="49">
-        <f t="shared" ref="C28:D28" si="2">C27/5</f>
+    <row r="28" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A28" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="38"/>
+      <c r="C28" s="27">
+        <f t="shared" ref="C28:D28" si="1">C27/5</f>
         <v>1</v>
       </c>
-      <c r="D28" s="49">
+      <c r="D28" s="27">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="24" customHeight="1">
+      <c r="A30" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+    </row>
+    <row r="31" spans="1:4" ht="24" customHeight="1">
+      <c r="A31" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A32" s="19">
+        <v>1</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="25"/>
+    </row>
+    <row r="33" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A33" s="19">
+        <v>2</v>
+      </c>
+      <c r="B33" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="25"/>
+    </row>
+    <row r="34" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A34" s="23">
+        <v>3</v>
+      </c>
+      <c r="B34" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="25"/>
+    </row>
+    <row r="35" spans="1:4" ht="24" customHeight="1">
+      <c r="A35" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="38"/>
+      <c r="C35" s="8">
+        <f>COUNTA('Hoja 1'!$C$32:$C$34)</f>
+        <v>3</v>
+      </c>
+      <c r="D35" s="8">
+        <f>COUNTA('Hoja 1'!$D$32:$D$34)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="24" customHeight="1">
+      <c r="A36" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="38"/>
+      <c r="C36" s="27">
+        <f t="shared" ref="C36:D36" si="2">C35/3</f>
+        <v>1</v>
+      </c>
+      <c r="D36" s="27">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="48"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="22"/>
-    </row>
-    <row r="30" ht="24.0" customHeight="1">
-      <c r="A30" s="35" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="31" ht="24.0" customHeight="1">
-      <c r="A31" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" ht="37.5" customHeight="1">
-      <c r="A32" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B32" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="47"/>
-    </row>
-    <row r="33" ht="37.5" customHeight="1">
-      <c r="A33" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B33" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="47"/>
-    </row>
-    <row r="34" ht="37.5" customHeight="1">
-      <c r="A34" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="B34" s="46" t="s">
+    <row r="37" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="38" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="39" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A40" s="51" t="s">
         <v>87</v>
       </c>
-      <c r="C34" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D34" s="47"/>
-    </row>
-    <row r="35" ht="24.0" customHeight="1">
-      <c r="A35" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="22">
-        <f>COUNTA('Hoja 1'!$C$32:$C$34)</f>
-        <v>3</v>
-      </c>
-      <c r="D35" s="22">
-        <f>COUNTA('Hoja 1'!$D$32:$D$34)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="24.0" customHeight="1">
-      <c r="A36" s="48" t="s">
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+    </row>
+    <row r="41" spans="1:4" ht="30" customHeight="1">
+      <c r="B41" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="30" customHeight="1">
+      <c r="B42" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="49">
-        <f t="shared" ref="C36:D36" si="3">C35/3</f>
-        <v>1</v>
-      </c>
-      <c r="D36" s="49">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="58" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="22">
-        <v>89.0</v>
-      </c>
-    </row>
-    <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="C44" s="22"/>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="C45" s="22"/>
-    </row>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+      <c r="C42" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="30" customHeight="1">
+      <c r="B43" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="14.25" customHeight="1">
+      <c r="C44" s="8"/>
+    </row>
+    <row r="45" spans="1:4" ht="14.25" customHeight="1">
+      <c r="C45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -6864,11 +7938,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="C1:D1"/>
@@ -6878,525 +7947,545 @@
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <conditionalFormatting sqref="D10 D16 A32:D34">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D10))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="12" priority="4" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="11" priority="5" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:D26">
-    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:D26">
-    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D10 D16 C32:D34">
-    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="8" priority="8" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(D10))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="3">
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.71"/>
-    <col customWidth="1" min="2" max="2" width="45.86"/>
-    <col customWidth="1" min="3" max="3" width="16.14"/>
-    <col customWidth="1" min="4" max="4" width="14.0"/>
-    <col customWidth="1" min="5" max="24" width="10.71"/>
+    <col min="1" max="1" width="10.7265625" customWidth="1"/>
+    <col min="2" max="2" width="45.81640625" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="24" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="51.0" customHeight="1">
-      <c r="A1" s="29"/>
-      <c r="B1" s="30" t="s">
+    <row r="1" spans="1:26" ht="51" customHeight="1">
+      <c r="A1" s="13"/>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="52" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="38"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+    </row>
+    <row r="2" spans="1:26" ht="17.25" customHeight="1">
+      <c r="B2" s="15" t="s">
         <v>55</v>
       </c>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-      <c r="S1" s="29"/>
-      <c r="T1" s="29"/>
-      <c r="U1" s="29"/>
-      <c r="V1" s="29"/>
-      <c r="W1" s="29"/>
-      <c r="X1" s="29"/>
-      <c r="Y1" s="29"/>
-      <c r="Z1" s="29"/>
-    </row>
-    <row r="2" ht="17.25" customHeight="1">
-      <c r="B2" s="32" t="s">
+      <c r="C2" s="53">
+        <v>46126</v>
+      </c>
+      <c r="D2" s="38"/>
+    </row>
+    <row r="3" spans="1:26" ht="20.25" customHeight="1">
+      <c r="B3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="33">
-        <v>46126.0</v>
-      </c>
-    </row>
-    <row r="3" ht="20.25" customHeight="1">
-      <c r="B3" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="B4" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" s="34" t="s">
+      <c r="C3" s="54" t="s">
+        <v>91</v>
+      </c>
+      <c r="D3" s="38"/>
+    </row>
+    <row r="4" spans="1:26" ht="18.75" customHeight="1">
+      <c r="B4" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="54" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="30.75" customHeight="1">
-      <c r="A6" s="35" t="s">
+      <c r="D4" s="38"/>
+    </row>
+    <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A6" s="50" t="s">
+        <v>60</v>
+      </c>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
+    </row>
+    <row r="7" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A7" s="16" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="7" ht="30.75" customHeight="1">
-      <c r="A7" s="36" t="s">
+      <c r="B7" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="C7" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="D7" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D7" s="38" t="s">
+    </row>
+    <row r="8" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A8" s="19">
+        <v>1</v>
+      </c>
+      <c r="B8" s="20" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" ht="30.75" customHeight="1">
-      <c r="A8" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="C8" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="41" t="s">
+      <c r="D8" s="22"/>
+    </row>
+    <row r="9" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A9" s="19">
+        <v>2</v>
+      </c>
+      <c r="B9" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="42"/>
-    </row>
-    <row r="9" ht="30.75" customHeight="1">
-      <c r="A9" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="40" t="s">
+      <c r="C9" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D9" s="22"/>
+    </row>
+    <row r="10" spans="1:26" ht="41.25" customHeight="1">
+      <c r="A10" s="19">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="42"/>
-    </row>
-    <row r="10" ht="41.25" customHeight="1">
-      <c r="A10" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="40" t="s">
+      <c r="C10" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D10" s="22"/>
+    </row>
+    <row r="11" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A11" s="19">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D10" s="42"/>
-    </row>
-    <row r="11" ht="30.75" customHeight="1">
-      <c r="A11" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="B11" s="40" t="s">
+      <c r="C11" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="22"/>
+    </row>
+    <row r="12" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A12" s="19">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="42"/>
-    </row>
-    <row r="12" ht="30.75" customHeight="1">
-      <c r="A12" s="39">
-        <v>5.0</v>
-      </c>
-      <c r="B12" s="40" t="s">
+      <c r="C12" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D12" s="22"/>
+    </row>
+    <row r="13" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A13" s="19">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="C12" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="42"/>
-    </row>
-    <row r="13" ht="30.75" customHeight="1">
-      <c r="A13" s="39">
-        <v>6.0</v>
-      </c>
-      <c r="B13" s="40" t="s">
+      <c r="C13" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="22"/>
+    </row>
+    <row r="14" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A14" s="19">
+        <v>7</v>
+      </c>
+      <c r="B14" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="C13" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="42"/>
-    </row>
-    <row r="14" ht="30.75" customHeight="1">
-      <c r="A14" s="39">
-        <v>7.0</v>
-      </c>
-      <c r="B14" s="40" t="s">
+      <c r="C14" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="22"/>
+    </row>
+    <row r="15" spans="1:26" ht="30.75" customHeight="1">
+      <c r="A15" s="19">
+        <v>8</v>
+      </c>
+      <c r="B15" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C14" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D14" s="42"/>
-    </row>
-    <row r="15" ht="30.75" customHeight="1">
-      <c r="A15" s="39">
-        <v>8.0</v>
-      </c>
-      <c r="B15" s="40" t="s">
+      <c r="C15" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" s="22"/>
+    </row>
+    <row r="16" spans="1:26" ht="54.75" customHeight="1">
+      <c r="A16" s="23">
+        <v>9</v>
+      </c>
+      <c r="B16" s="24" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="41" t="s">
-        <v>67</v>
-      </c>
-      <c r="D15" s="42"/>
-    </row>
-    <row r="16" ht="54.75" customHeight="1">
-      <c r="A16" s="45">
-        <v>9.0</v>
-      </c>
-      <c r="B16" s="46" t="s">
+      <c r="C16" s="25"/>
+      <c r="D16" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A17" s="49" t="s">
         <v>75</v>
       </c>
-      <c r="C16" s="47"/>
-      <c r="D16" s="47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" ht="20.25" customHeight="1">
-      <c r="A17" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" s="22">
+      <c r="B17" s="38"/>
+      <c r="C17" s="8">
         <f>COUNTA('Hoja 2'!$C$8:$C$16)</f>
         <v>8</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="8">
         <f>COUNTA('Hoja 2'!$D$8:$D$16)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="20.25" customHeight="1">
-      <c r="A18" s="48" t="s">
+    <row r="18" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A18" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B18" s="38"/>
+      <c r="C18" s="27">
+        <f t="shared" ref="C18:D18" si="0">C17/9</f>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="D18" s="27">
+        <f t="shared" si="0"/>
+        <v>0.1111111111111111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="27"/>
+      <c r="D19" s="8"/>
+    </row>
+    <row r="20" spans="1:4" ht="25.5" customHeight="1">
+      <c r="A20" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="49">
-        <f t="shared" ref="C18:D18" si="1">C17/9</f>
-        <v>0.8888888889</v>
-      </c>
-      <c r="D18" s="49">
-        <f t="shared" si="1"/>
-        <v>0.1111111111</v>
-      </c>
-    </row>
-    <row r="19" ht="14.25" customHeight="1">
-      <c r="A19" s="48"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="22"/>
-    </row>
-    <row r="20" ht="25.5" customHeight="1">
-      <c r="A20" s="50" t="s">
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
+      <c r="D20" s="56"/>
+    </row>
+    <row r="21" spans="1:4" ht="20.25" customHeight="1">
+      <c r="A21" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D21" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="32.25" customHeight="1">
+      <c r="A22" s="19">
+        <v>1</v>
+      </c>
+      <c r="B22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B20" s="51"/>
-      <c r="C20" s="51"/>
-      <c r="D20" s="51"/>
-    </row>
-    <row r="21" ht="20.25" customHeight="1">
-      <c r="A21" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="B21" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" ht="32.25" customHeight="1">
-      <c r="A22" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B22" s="40" t="s">
+      <c r="C22" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="22"/>
+    </row>
+    <row r="23" spans="1:4" ht="14.5">
+      <c r="A23" s="19">
+        <v>2</v>
+      </c>
+      <c r="B23" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D22" s="42"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B23" s="40" t="s">
+      <c r="C23" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D23" s="22"/>
+    </row>
+    <row r="24" spans="1:4" ht="14.5">
+      <c r="A24" s="19">
+        <v>3</v>
+      </c>
+      <c r="B24" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="C23" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="42"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="39">
-        <v>3.0</v>
-      </c>
-      <c r="B24" s="40" t="s">
+      <c r="C24" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D24" s="22"/>
+    </row>
+    <row r="25" spans="1:4" ht="34.5" customHeight="1">
+      <c r="A25" s="19">
+        <v>4</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C24" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D24" s="42"/>
-    </row>
-    <row r="25" ht="34.5" customHeight="1">
-      <c r="A25" s="39">
-        <v>4.0</v>
-      </c>
-      <c r="B25" s="40" t="s">
+      <c r="C25" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="22"/>
+    </row>
+    <row r="26" spans="1:4" ht="40.5" customHeight="1">
+      <c r="A26" s="23">
+        <v>5</v>
+      </c>
+      <c r="B26" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="42"/>
-    </row>
-    <row r="26" ht="40.5" customHeight="1">
-      <c r="A26" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="B26" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="56"/>
-    </row>
-    <row r="27" ht="24.75" customHeight="1">
-      <c r="A27" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C27" s="22">
+      <c r="C26" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="32"/>
+    </row>
+    <row r="27" spans="1:4" ht="24.75" customHeight="1">
+      <c r="A27" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B27" s="38"/>
+      <c r="C27" s="8">
         <f>COUNTA('Hoja 2'!$C$22:$C$26)</f>
         <v>5</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="8">
         <f>COUNTA('Hoja 2'!$D$22:$D$26)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="28.5" customHeight="1">
-      <c r="A28" s="48" t="s">
-        <v>77</v>
-      </c>
-      <c r="C28" s="49">
-        <f t="shared" ref="C28:D28" si="2">C27/5</f>
+    <row r="28" spans="1:4" ht="28.5" customHeight="1">
+      <c r="A28" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="38"/>
+      <c r="C28" s="27">
+        <f t="shared" ref="C28:D28" si="1">C27/5</f>
         <v>1</v>
       </c>
-      <c r="D28" s="49">
-        <f t="shared" si="2"/>
+      <c r="D28" s="27">
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="48"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="49"/>
-      <c r="D29" s="22"/>
-    </row>
-    <row r="30" ht="24.0" customHeight="1">
-      <c r="A30" s="35" t="s">
+    <row r="29" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A29" s="26"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="27"/>
+      <c r="D29" s="8"/>
+    </row>
+    <row r="30" spans="1:4" ht="24" customHeight="1">
+      <c r="A30" s="50" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+    </row>
+    <row r="31" spans="1:4" ht="24" customHeight="1">
+      <c r="A31" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="29" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A32" s="19">
+        <v>1</v>
+      </c>
+      <c r="B32" s="20" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="31" ht="24.0" customHeight="1">
-      <c r="A31" s="52" t="s">
-        <v>62</v>
-      </c>
-      <c r="B31" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="C31" s="54" t="s">
-        <v>64</v>
-      </c>
-      <c r="D31" s="55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" ht="37.5" customHeight="1">
-      <c r="A32" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B32" s="40" t="s">
+      <c r="C32" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="25"/>
+    </row>
+    <row r="33" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A33" s="19">
+        <v>2</v>
+      </c>
+      <c r="B33" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C32" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="47"/>
-    </row>
-    <row r="33" ht="37.5" customHeight="1">
-      <c r="A33" s="39">
-        <v>2.0</v>
-      </c>
-      <c r="B33" s="40" t="s">
+      <c r="C33" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="25"/>
+    </row>
+    <row r="34" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A34" s="23">
+        <v>3</v>
+      </c>
+      <c r="B34" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="C33" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="D33" s="47"/>
-    </row>
-    <row r="34" ht="37.5" customHeight="1">
-      <c r="A34" s="45">
-        <v>3.0</v>
-      </c>
-      <c r="B34" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="47"/>
-      <c r="D34" s="47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" ht="24.0" customHeight="1">
-      <c r="A35" s="48" t="s">
-        <v>76</v>
-      </c>
-      <c r="C35" s="22">
+      <c r="C34" s="25"/>
+      <c r="D34" s="25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="24" customHeight="1">
+      <c r="A35" s="49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="38"/>
+      <c r="C35" s="8">
         <f>COUNTA('Hoja 2'!$C$32:$C$34)</f>
         <v>2</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="8">
         <f>COUNTA('Hoja 2'!$D$32:$D$34)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="36" ht="24.0" customHeight="1">
-      <c r="A36" s="48" t="s">
+    <row r="36" spans="1:4" ht="24" customHeight="1">
+      <c r="A36" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="38"/>
+      <c r="C36" s="27">
+        <f t="shared" ref="C36:D36" si="2">C35/3</f>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="D36" s="27">
+        <f t="shared" si="2"/>
+        <v>0.33333333333333331</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="38" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="39" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="40" spans="1:4" ht="14.25" customHeight="1">
+      <c r="A40" s="51" t="s">
+        <v>87</v>
+      </c>
+      <c r="B40" s="38"/>
+      <c r="C40" s="38"/>
+    </row>
+    <row r="41" spans="1:4" ht="30" customHeight="1">
+      <c r="B41" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="8">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="30" customHeight="1">
+      <c r="B42" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="49">
-        <f t="shared" ref="C36:D36" si="3">C35/3</f>
-        <v>0.6666666667</v>
-      </c>
-      <c r="D36" s="49">
-        <f t="shared" si="3"/>
-        <v>0.3333333333</v>
-      </c>
-    </row>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1">
-      <c r="A40" s="58" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="41" ht="30.0" customHeight="1">
-      <c r="B41" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="22">
-        <v>89.0</v>
-      </c>
-    </row>
-    <row r="42" ht="30.0" customHeight="1">
-      <c r="B42" s="29" t="s">
-        <v>78</v>
-      </c>
-      <c r="C42" s="22">
-        <v>100.0</v>
-      </c>
-    </row>
-    <row r="43" ht="30.0" customHeight="1">
-      <c r="B43" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="59">
-        <v>67.0</v>
-      </c>
-    </row>
-    <row r="44" ht="14.25" customHeight="1">
-      <c r="C44" s="22"/>
-    </row>
-    <row r="45" ht="14.25" customHeight="1">
-      <c r="C45" s="22"/>
-    </row>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
+      <c r="C42" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="30" customHeight="1">
+      <c r="B43" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="8">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="14.25" customHeight="1">
+      <c r="C44" s="8"/>
+    </row>
+    <row r="45" spans="1:4" ht="14.25" customHeight="1">
+      <c r="C45" s="8"/>
+    </row>
+    <row r="46" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="47" spans="1:4" ht="14.25" customHeight="1"/>
+    <row r="48" spans="1:4" ht="14.25" customHeight="1"/>
     <row r="49" ht="14.25" customHeight="1"/>
     <row r="50" ht="14.25" customHeight="1"/>
     <row r="51" ht="14.25" customHeight="1"/>
@@ -8351,11 +9440,6 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A35:B35"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="C1:D1"/>
@@ -8365,109 +9449,1156 @@
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <conditionalFormatting sqref="A32:D34">
-    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(A32))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="9" priority="2" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="10" priority="3" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="11" priority="4" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C8:D16 C22:C26 C32:D34">
-    <cfRule type="containsText" dxfId="12" priority="5" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C8))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:D26">
-    <cfRule type="containsText" dxfId="9" priority="6" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C22:D26">
-    <cfRule type="containsText" dxfId="10" priority="7" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C22))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C32:D34">
-    <cfRule type="containsText" dxfId="9" priority="8" operator="containsText" text="X">
+    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="X">
       <formula>NOT(ISERROR(SEARCH(("X"),(C32))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId2"/>
-  <legacyDrawing r:id="rId3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="3">
-    <tablePart r:id="rId7"/>
-    <tablePart r:id="rId8"/>
-    <tablePart r:id="rId9"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:B1001"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="53.14"/>
-    <col customWidth="1" min="2" max="2" width="57.29"/>
-    <col customWidth="1" min="3" max="6" width="10.71"/>
+    <col min="1" max="1" width="53.08984375" customWidth="1"/>
+    <col min="2" max="2" width="57.26953125" customWidth="1"/>
+    <col min="3" max="6" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="60" t="s">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A1" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="60" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="58">
+      <c r="A2" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="82" customHeight="1">
+      <c r="A3" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="72.5">
+      <c r="A4" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="8" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="17" ht="14.25" customHeight="1"/>
+    <row r="18" ht="14.25" customHeight="1"/>
+    <row r="19" ht="14.25" customHeight="1"/>
+    <row r="20" ht="14.25" customHeight="1"/>
+    <row r="21" ht="14.25" customHeight="1"/>
+    <row r="22" ht="14.25" customHeight="1"/>
+    <row r="23" ht="14.25" customHeight="1"/>
+    <row r="24" ht="14.25" customHeight="1"/>
+    <row r="25" ht="14.25" customHeight="1"/>
+    <row r="26" ht="14.25" customHeight="1"/>
+    <row r="27" ht="14.25" customHeight="1"/>
+    <row r="28" ht="14.25" customHeight="1"/>
+    <row r="29" ht="14.25" customHeight="1"/>
+    <row r="30" ht="14.25" customHeight="1"/>
+    <row r="31" ht="14.25" customHeight="1"/>
+    <row r="32" ht="14.25" customHeight="1"/>
+    <row r="33" ht="14.25" customHeight="1"/>
+    <row r="34" ht="14.25" customHeight="1"/>
+    <row r="35" ht="14.25" customHeight="1"/>
+    <row r="36" ht="14.25" customHeight="1"/>
+    <row r="37" ht="14.25" customHeight="1"/>
+    <row r="38" ht="14.25" customHeight="1"/>
+    <row r="39" ht="14.25" customHeight="1"/>
+    <row r="40" ht="14.25" customHeight="1"/>
+    <row r="41" ht="14.25" customHeight="1"/>
+    <row r="42" ht="14.25" customHeight="1"/>
+    <row r="43" ht="14.25" customHeight="1"/>
+    <row r="44" ht="14.25" customHeight="1"/>
+    <row r="45" ht="14.25" customHeight="1"/>
+    <row r="46" ht="14.25" customHeight="1"/>
+    <row r="47" ht="14.25" customHeight="1"/>
+    <row r="48" ht="14.25" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="53" ht="14.25" customHeight="1"/>
+    <row r="54" ht="14.25" customHeight="1"/>
+    <row r="55" ht="14.25" customHeight="1"/>
+    <row r="56" ht="14.25" customHeight="1"/>
+    <row r="57" ht="14.25" customHeight="1"/>
+    <row r="58" ht="14.25" customHeight="1"/>
+    <row r="59" ht="14.25" customHeight="1"/>
+    <row r="60" ht="14.25" customHeight="1"/>
+    <row r="61" ht="14.25" customHeight="1"/>
+    <row r="62" ht="14.25" customHeight="1"/>
+    <row r="63" ht="14.25" customHeight="1"/>
+    <row r="64" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
+    <row r="95" ht="14.25" customHeight="1"/>
+    <row r="96" ht="14.25" customHeight="1"/>
+    <row r="97" ht="14.25" customHeight="1"/>
+    <row r="98" ht="14.25" customHeight="1"/>
+    <row r="99" ht="14.25" customHeight="1"/>
+    <row r="100" ht="14.25" customHeight="1"/>
+    <row r="101" ht="14.25" customHeight="1"/>
+    <row r="102" ht="14.25" customHeight="1"/>
+    <row r="103" ht="14.25" customHeight="1"/>
+    <row r="104" ht="14.25" customHeight="1"/>
+    <row r="105" ht="14.25" customHeight="1"/>
+    <row r="106" ht="14.25" customHeight="1"/>
+    <row r="107" ht="14.25" customHeight="1"/>
+    <row r="108" ht="14.25" customHeight="1"/>
+    <row r="109" ht="14.25" customHeight="1"/>
+    <row r="110" ht="14.25" customHeight="1"/>
+    <row r="111" ht="14.25" customHeight="1"/>
+    <row r="112" ht="14.25" customHeight="1"/>
+    <row r="113" ht="14.25" customHeight="1"/>
+    <row r="114" ht="14.25" customHeight="1"/>
+    <row r="115" ht="14.25" customHeight="1"/>
+    <row r="116" ht="14.25" customHeight="1"/>
+    <row r="117" ht="14.25" customHeight="1"/>
+    <row r="118" ht="14.25" customHeight="1"/>
+    <row r="119" ht="14.25" customHeight="1"/>
+    <row r="120" ht="14.25" customHeight="1"/>
+    <row r="121" ht="14.25" customHeight="1"/>
+    <row r="122" ht="14.25" customHeight="1"/>
+    <row r="123" ht="14.25" customHeight="1"/>
+    <row r="124" ht="14.25" customHeight="1"/>
+    <row r="125" ht="14.25" customHeight="1"/>
+    <row r="126" ht="14.25" customHeight="1"/>
+    <row r="127" ht="14.25" customHeight="1"/>
+    <row r="128" ht="14.25" customHeight="1"/>
+    <row r="129" ht="14.25" customHeight="1"/>
+    <row r="130" ht="14.25" customHeight="1"/>
+    <row r="131" ht="14.25" customHeight="1"/>
+    <row r="132" ht="14.25" customHeight="1"/>
+    <row r="133" ht="14.25" customHeight="1"/>
+    <row r="134" ht="14.25" customHeight="1"/>
+    <row r="135" ht="14.25" customHeight="1"/>
+    <row r="136" ht="14.25" customHeight="1"/>
+    <row r="137" ht="14.25" customHeight="1"/>
+    <row r="138" ht="14.25" customHeight="1"/>
+    <row r="139" ht="14.25" customHeight="1"/>
+    <row r="140" ht="14.25" customHeight="1"/>
+    <row r="141" ht="14.25" customHeight="1"/>
+    <row r="142" ht="14.25" customHeight="1"/>
+    <row r="143" ht="14.25" customHeight="1"/>
+    <row r="144" ht="14.25" customHeight="1"/>
+    <row r="145" ht="14.25" customHeight="1"/>
+    <row r="146" ht="14.25" customHeight="1"/>
+    <row r="147" ht="14.25" customHeight="1"/>
+    <row r="148" ht="14.25" customHeight="1"/>
+    <row r="149" ht="14.25" customHeight="1"/>
+    <row r="150" ht="14.25" customHeight="1"/>
+    <row r="151" ht="14.25" customHeight="1"/>
+    <row r="152" ht="14.25" customHeight="1"/>
+    <row r="153" ht="14.25" customHeight="1"/>
+    <row r="154" ht="14.25" customHeight="1"/>
+    <row r="155" ht="14.25" customHeight="1"/>
+    <row r="156" ht="14.25" customHeight="1"/>
+    <row r="157" ht="14.25" customHeight="1"/>
+    <row r="158" ht="14.25" customHeight="1"/>
+    <row r="159" ht="14.25" customHeight="1"/>
+    <row r="160" ht="14.25" customHeight="1"/>
+    <row r="161" ht="14.25" customHeight="1"/>
+    <row r="162" ht="14.25" customHeight="1"/>
+    <row r="163" ht="14.25" customHeight="1"/>
+    <row r="164" ht="14.25" customHeight="1"/>
+    <row r="165" ht="14.25" customHeight="1"/>
+    <row r="166" ht="14.25" customHeight="1"/>
+    <row r="167" ht="14.25" customHeight="1"/>
+    <row r="168" ht="14.25" customHeight="1"/>
+    <row r="169" ht="14.25" customHeight="1"/>
+    <row r="170" ht="14.25" customHeight="1"/>
+    <row r="171" ht="14.25" customHeight="1"/>
+    <row r="172" ht="14.25" customHeight="1"/>
+    <row r="173" ht="14.25" customHeight="1"/>
+    <row r="174" ht="14.25" customHeight="1"/>
+    <row r="175" ht="14.25" customHeight="1"/>
+    <row r="176" ht="14.25" customHeight="1"/>
+    <row r="177" ht="14.25" customHeight="1"/>
+    <row r="178" ht="14.25" customHeight="1"/>
+    <row r="179" ht="14.25" customHeight="1"/>
+    <row r="180" ht="14.25" customHeight="1"/>
+    <row r="181" ht="14.25" customHeight="1"/>
+    <row r="182" ht="14.25" customHeight="1"/>
+    <row r="183" ht="14.25" customHeight="1"/>
+    <row r="184" ht="14.25" customHeight="1"/>
+    <row r="185" ht="14.25" customHeight="1"/>
+    <row r="186" ht="14.25" customHeight="1"/>
+    <row r="187" ht="14.25" customHeight="1"/>
+    <row r="188" ht="14.25" customHeight="1"/>
+    <row r="189" ht="14.25" customHeight="1"/>
+    <row r="190" ht="14.25" customHeight="1"/>
+    <row r="191" ht="14.25" customHeight="1"/>
+    <row r="192" ht="14.25" customHeight="1"/>
+    <row r="193" ht="14.25" customHeight="1"/>
+    <row r="194" ht="14.25" customHeight="1"/>
+    <row r="195" ht="14.25" customHeight="1"/>
+    <row r="196" ht="14.25" customHeight="1"/>
+    <row r="197" ht="14.25" customHeight="1"/>
+    <row r="198" ht="14.25" customHeight="1"/>
+    <row r="199" ht="14.25" customHeight="1"/>
+    <row r="200" ht="14.25" customHeight="1"/>
+    <row r="201" ht="14.25" customHeight="1"/>
+    <row r="202" ht="14.25" customHeight="1"/>
+    <row r="203" ht="14.25" customHeight="1"/>
+    <row r="204" ht="14.25" customHeight="1"/>
+    <row r="205" ht="14.25" customHeight="1"/>
+    <row r="206" ht="14.25" customHeight="1"/>
+    <row r="207" ht="14.25" customHeight="1"/>
+    <row r="208" ht="14.25" customHeight="1"/>
+    <row r="209" ht="14.25" customHeight="1"/>
+    <row r="210" ht="14.25" customHeight="1"/>
+    <row r="211" ht="14.25" customHeight="1"/>
+    <row r="212" ht="14.25" customHeight="1"/>
+    <row r="213" ht="14.25" customHeight="1"/>
+    <row r="214" ht="14.25" customHeight="1"/>
+    <row r="215" ht="14.25" customHeight="1"/>
+    <row r="216" ht="14.25" customHeight="1"/>
+    <row r="217" ht="14.25" customHeight="1"/>
+    <row r="218" ht="14.25" customHeight="1"/>
+    <row r="219" ht="14.25" customHeight="1"/>
+    <row r="220" ht="14.25" customHeight="1"/>
+    <row r="221" ht="14.25" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="809" ht="15.75" customHeight="1"/>
+    <row r="810" ht="15.75" customHeight="1"/>
+    <row r="811" ht="15.75" customHeight="1"/>
+    <row r="812" ht="15.75" customHeight="1"/>
+    <row r="813" ht="15.75" customHeight="1"/>
+    <row r="814" ht="15.75" customHeight="1"/>
+    <row r="815" ht="15.75" customHeight="1"/>
+    <row r="816" ht="15.75" customHeight="1"/>
+    <row r="817" ht="15.75" customHeight="1"/>
+    <row r="818" ht="15.75" customHeight="1"/>
+    <row r="819" ht="15.75" customHeight="1"/>
+    <row r="820" ht="15.75" customHeight="1"/>
+    <row r="821" ht="15.75" customHeight="1"/>
+    <row r="822" ht="15.75" customHeight="1"/>
+    <row r="823" ht="15.75" customHeight="1"/>
+    <row r="824" ht="15.75" customHeight="1"/>
+    <row r="825" ht="15.75" customHeight="1"/>
+    <row r="826" ht="15.75" customHeight="1"/>
+    <row r="827" ht="15.75" customHeight="1"/>
+    <row r="828" ht="15.75" customHeight="1"/>
+    <row r="829" ht="15.75" customHeight="1"/>
+    <row r="830" ht="15.75" customHeight="1"/>
+    <row r="831" ht="15.75" customHeight="1"/>
+    <row r="832" ht="15.75" customHeight="1"/>
+    <row r="833" ht="15.75" customHeight="1"/>
+    <row r="834" ht="15.75" customHeight="1"/>
+    <row r="835" ht="15.75" customHeight="1"/>
+    <row r="836" ht="15.75" customHeight="1"/>
+    <row r="837" ht="15.75" customHeight="1"/>
+    <row r="838" ht="15.75" customHeight="1"/>
+    <row r="839" ht="15.75" customHeight="1"/>
+    <row r="840" ht="15.75" customHeight="1"/>
+    <row r="841" ht="15.75" customHeight="1"/>
+    <row r="842" ht="15.75" customHeight="1"/>
+    <row r="843" ht="15.75" customHeight="1"/>
+    <row r="844" ht="15.75" customHeight="1"/>
+    <row r="845" ht="15.75" customHeight="1"/>
+    <row r="846" ht="15.75" customHeight="1"/>
+    <row r="847" ht="15.75" customHeight="1"/>
+    <row r="848" ht="15.75" customHeight="1"/>
+    <row r="849" ht="15.75" customHeight="1"/>
+    <row r="850" ht="15.75" customHeight="1"/>
+    <row r="851" ht="15.75" customHeight="1"/>
+    <row r="852" ht="15.75" customHeight="1"/>
+    <row r="853" ht="15.75" customHeight="1"/>
+    <row r="854" ht="15.75" customHeight="1"/>
+    <row r="855" ht="15.75" customHeight="1"/>
+    <row r="856" ht="15.75" customHeight="1"/>
+    <row r="857" ht="15.75" customHeight="1"/>
+    <row r="858" ht="15.75" customHeight="1"/>
+    <row r="859" ht="15.75" customHeight="1"/>
+    <row r="860" ht="15.75" customHeight="1"/>
+    <row r="861" ht="15.75" customHeight="1"/>
+    <row r="862" ht="15.75" customHeight="1"/>
+    <row r="863" ht="15.75" customHeight="1"/>
+    <row r="864" ht="15.75" customHeight="1"/>
+    <row r="865" ht="15.75" customHeight="1"/>
+    <row r="866" ht="15.75" customHeight="1"/>
+    <row r="867" ht="15.75" customHeight="1"/>
+    <row r="868" ht="15.75" customHeight="1"/>
+    <row r="869" ht="15.75" customHeight="1"/>
+    <row r="870" ht="15.75" customHeight="1"/>
+    <row r="871" ht="15.75" customHeight="1"/>
+    <row r="872" ht="15.75" customHeight="1"/>
+    <row r="873" ht="15.75" customHeight="1"/>
+    <row r="874" ht="15.75" customHeight="1"/>
+    <row r="875" ht="15.75" customHeight="1"/>
+    <row r="876" ht="15.75" customHeight="1"/>
+    <row r="877" ht="15.75" customHeight="1"/>
+    <row r="878" ht="15.75" customHeight="1"/>
+    <row r="879" ht="15.75" customHeight="1"/>
+    <row r="880" ht="15.75" customHeight="1"/>
+    <row r="881" ht="15.75" customHeight="1"/>
+    <row r="882" ht="15.75" customHeight="1"/>
+    <row r="883" ht="15.75" customHeight="1"/>
+    <row r="884" ht="15.75" customHeight="1"/>
+    <row r="885" ht="15.75" customHeight="1"/>
+    <row r="886" ht="15.75" customHeight="1"/>
+    <row r="887" ht="15.75" customHeight="1"/>
+    <row r="888" ht="15.75" customHeight="1"/>
+    <row r="889" ht="15.75" customHeight="1"/>
+    <row r="890" ht="15.75" customHeight="1"/>
+    <row r="891" ht="15.75" customHeight="1"/>
+    <row r="892" ht="15.75" customHeight="1"/>
+    <row r="893" ht="15.75" customHeight="1"/>
+    <row r="894" ht="15.75" customHeight="1"/>
+    <row r="895" ht="15.75" customHeight="1"/>
+    <row r="896" ht="15.75" customHeight="1"/>
+    <row r="897" ht="15.75" customHeight="1"/>
+    <row r="898" ht="15.75" customHeight="1"/>
+    <row r="899" ht="15.75" customHeight="1"/>
+    <row r="900" ht="15.75" customHeight="1"/>
+    <row r="901" ht="15.75" customHeight="1"/>
+    <row r="902" ht="15.75" customHeight="1"/>
+    <row r="903" ht="15.75" customHeight="1"/>
+    <row r="904" ht="15.75" customHeight="1"/>
+    <row r="905" ht="15.75" customHeight="1"/>
+    <row r="906" ht="15.75" customHeight="1"/>
+    <row r="907" ht="15.75" customHeight="1"/>
+    <row r="908" ht="15.75" customHeight="1"/>
+    <row r="909" ht="15.75" customHeight="1"/>
+    <row r="910" ht="15.75" customHeight="1"/>
+    <row r="911" ht="15.75" customHeight="1"/>
+    <row r="912" ht="15.75" customHeight="1"/>
+    <row r="913" ht="15.75" customHeight="1"/>
+    <row r="914" ht="15.75" customHeight="1"/>
+    <row r="915" ht="15.75" customHeight="1"/>
+    <row r="916" ht="15.75" customHeight="1"/>
+    <row r="917" ht="15.75" customHeight="1"/>
+    <row r="918" ht="15.75" customHeight="1"/>
+    <row r="919" ht="15.75" customHeight="1"/>
+    <row r="920" ht="15.75" customHeight="1"/>
+    <row r="921" ht="15.75" customHeight="1"/>
+    <row r="922" ht="15.75" customHeight="1"/>
+    <row r="923" ht="15.75" customHeight="1"/>
+    <row r="924" ht="15.75" customHeight="1"/>
+    <row r="925" ht="15.75" customHeight="1"/>
+    <row r="926" ht="15.75" customHeight="1"/>
+    <row r="927" ht="15.75" customHeight="1"/>
+    <row r="928" ht="15.75" customHeight="1"/>
+    <row r="929" ht="15.75" customHeight="1"/>
+    <row r="930" ht="15.75" customHeight="1"/>
+    <row r="931" ht="15.75" customHeight="1"/>
+    <row r="932" ht="15.75" customHeight="1"/>
+    <row r="933" ht="15.75" customHeight="1"/>
+    <row r="934" ht="15.75" customHeight="1"/>
+    <row r="935" ht="15.75" customHeight="1"/>
+    <row r="936" ht="15.75" customHeight="1"/>
+    <row r="937" ht="15.75" customHeight="1"/>
+    <row r="938" ht="15.75" customHeight="1"/>
+    <row r="939" ht="15.75" customHeight="1"/>
+    <row r="940" ht="15.75" customHeight="1"/>
+    <row r="941" ht="15.75" customHeight="1"/>
+    <row r="942" ht="15.75" customHeight="1"/>
+    <row r="943" ht="15.75" customHeight="1"/>
+    <row r="944" ht="15.75" customHeight="1"/>
+    <row r="945" ht="15.75" customHeight="1"/>
+    <row r="946" ht="15.75" customHeight="1"/>
+    <row r="947" ht="15.75" customHeight="1"/>
+    <row r="948" ht="15.75" customHeight="1"/>
+    <row r="949" ht="15.75" customHeight="1"/>
+    <row r="950" ht="15.75" customHeight="1"/>
+    <row r="951" ht="15.75" customHeight="1"/>
+    <row r="952" ht="15.75" customHeight="1"/>
+    <row r="953" ht="15.75" customHeight="1"/>
+    <row r="954" ht="15.75" customHeight="1"/>
+    <row r="955" ht="15.75" customHeight="1"/>
+    <row r="956" ht="15.75" customHeight="1"/>
+    <row r="957" ht="15.75" customHeight="1"/>
+    <row r="958" ht="15.75" customHeight="1"/>
+    <row r="959" ht="15.75" customHeight="1"/>
+    <row r="960" ht="15.75" customHeight="1"/>
+    <row r="961" ht="15.75" customHeight="1"/>
+    <row r="962" ht="15.75" customHeight="1"/>
+    <row r="963" ht="15.75" customHeight="1"/>
+    <row r="964" ht="15.75" customHeight="1"/>
+    <row r="965" ht="15.75" customHeight="1"/>
+    <row r="966" ht="15.75" customHeight="1"/>
+    <row r="967" ht="15.75" customHeight="1"/>
+    <row r="968" ht="15.75" customHeight="1"/>
+    <row r="969" ht="15.75" customHeight="1"/>
+    <row r="970" ht="15.75" customHeight="1"/>
+    <row r="971" ht="15.75" customHeight="1"/>
+    <row r="972" ht="15.75" customHeight="1"/>
+    <row r="973" ht="15.75" customHeight="1"/>
+    <row r="974" ht="15.75" customHeight="1"/>
+    <row r="975" ht="15.75" customHeight="1"/>
+    <row r="976" ht="15.75" customHeight="1"/>
+    <row r="977" ht="15.75" customHeight="1"/>
+    <row r="978" ht="15.75" customHeight="1"/>
+    <row r="979" ht="15.75" customHeight="1"/>
+    <row r="980" ht="15.75" customHeight="1"/>
+    <row r="981" ht="15.75" customHeight="1"/>
+    <row r="982" ht="15.75" customHeight="1"/>
+    <row r="983" ht="15.75" customHeight="1"/>
+    <row r="984" ht="15.75" customHeight="1"/>
+    <row r="985" ht="15.75" customHeight="1"/>
+    <row r="986" ht="15.75" customHeight="1"/>
+    <row r="987" ht="15.75" customHeight="1"/>
+    <row r="988" ht="15.75" customHeight="1"/>
+    <row r="989" ht="15.75" customHeight="1"/>
+    <row r="990" ht="15.75" customHeight="1"/>
+    <row r="991" ht="15.75" customHeight="1"/>
+    <row r="992" ht="15.75" customHeight="1"/>
+    <row r="993" ht="15.75" customHeight="1"/>
+    <row r="994" ht="15.75" customHeight="1"/>
+    <row r="995" ht="15.75" customHeight="1"/>
+    <row r="996" ht="15.75" customHeight="1"/>
+    <row r="997" ht="15.75" customHeight="1"/>
+    <row r="998" ht="15.75" customHeight="1"/>
+    <row r="999" ht="15.75" customHeight="1"/>
+    <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup orientation="landscape"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:B1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="53.08984375" customWidth="1"/>
+    <col min="2" max="2" width="57.26953125" customWidth="1"/>
+    <col min="3" max="6" width="10.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A1" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="58">
+      <c r="A2" s="20" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="61" t="s">
+      <c r="B2" s="20" t="s">
         <v>95</v>
       </c>
-      <c r="B2" s="62" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="58">
+      <c r="A3" s="4" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="B3" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="B3" s="62" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
+    </row>
+    <row r="4" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="8" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -9453,62 +11584,65 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:B1000"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="53.14"/>
-    <col customWidth="1" min="2" max="2" width="57.29"/>
-    <col customWidth="1" min="3" max="6" width="10.71"/>
+    <col min="1" max="1" width="53.08984375" customWidth="1"/>
+    <col min="2" max="2" width="57.26953125" customWidth="1"/>
+    <col min="3" max="6" width="10.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="60" t="s">
+    <row r="1" spans="1:2" ht="14.25" customHeight="1">
+      <c r="A1" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="60" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="61" t="s">
-        <v>95</v>
-      </c>
-      <c r="B2" s="62" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B3" s="62" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="58">
+      <c r="A2" s="20" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="4" ht="14.25" customHeight="1"/>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
+      <c r="B2" s="20" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="29">
+      <c r="A3" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="44.25" customHeight="1">
+      <c r="A4" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="6" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="7" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="8" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="9" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="10" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="11" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="12" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="13" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="14" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="15" spans="1:2" ht="14.25" customHeight="1"/>
+    <row r="16" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="17" ht="14.25" customHeight="1"/>
     <row r="18" ht="14.25" customHeight="1"/>
     <row r="19" ht="14.25" customHeight="1"/>
@@ -10494,1057 +12628,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="53.14"/>
-    <col customWidth="1" min="2" max="2" width="57.29"/>
-    <col customWidth="1" min="3" max="6" width="10.71"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="14.25" customHeight="1">
-      <c r="A1" s="60" t="s">
-        <v>93</v>
-      </c>
-      <c r="B1" s="60" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="62" t="s">
-        <v>99</v>
-      </c>
-      <c r="B2" s="62" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="62" t="s">
-        <v>101</v>
-      </c>
-      <c r="B3" s="62" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" ht="44.25" customHeight="1">
-      <c r="A4" s="62" t="s">
-        <v>103</v>
-      </c>
-      <c r="B4" s="62" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" ht="14.25" customHeight="1"/>
-    <row r="6" ht="14.25" customHeight="1"/>
-    <row r="7" ht="14.25" customHeight="1"/>
-    <row r="8" ht="14.25" customHeight="1"/>
-    <row r="9" ht="14.25" customHeight="1"/>
-    <row r="10" ht="14.25" customHeight="1"/>
-    <row r="11" ht="14.25" customHeight="1"/>
-    <row r="12" ht="14.25" customHeight="1"/>
-    <row r="13" ht="14.25" customHeight="1"/>
-    <row r="14" ht="14.25" customHeight="1"/>
-    <row r="15" ht="14.25" customHeight="1"/>
-    <row r="16" ht="14.25" customHeight="1"/>
-    <row r="17" ht="14.25" customHeight="1"/>
-    <row r="18" ht="14.25" customHeight="1"/>
-    <row r="19" ht="14.25" customHeight="1"/>
-    <row r="20" ht="14.25" customHeight="1"/>
-    <row r="21" ht="14.25" customHeight="1"/>
-    <row r="22" ht="14.25" customHeight="1"/>
-    <row r="23" ht="14.25" customHeight="1"/>
-    <row r="24" ht="14.25" customHeight="1"/>
-    <row r="25" ht="14.25" customHeight="1"/>
-    <row r="26" ht="14.25" customHeight="1"/>
-    <row r="27" ht="14.25" customHeight="1"/>
-    <row r="28" ht="14.25" customHeight="1"/>
-    <row r="29" ht="14.25" customHeight="1"/>
-    <row r="30" ht="14.25" customHeight="1"/>
-    <row r="31" ht="14.25" customHeight="1"/>
-    <row r="32" ht="14.25" customHeight="1"/>
-    <row r="33" ht="14.25" customHeight="1"/>
-    <row r="34" ht="14.25" customHeight="1"/>
-    <row r="35" ht="14.25" customHeight="1"/>
-    <row r="36" ht="14.25" customHeight="1"/>
-    <row r="37" ht="14.25" customHeight="1"/>
-    <row r="38" ht="14.25" customHeight="1"/>
-    <row r="39" ht="14.25" customHeight="1"/>
-    <row r="40" ht="14.25" customHeight="1"/>
-    <row r="41" ht="14.25" customHeight="1"/>
-    <row r="42" ht="14.25" customHeight="1"/>
-    <row r="43" ht="14.25" customHeight="1"/>
-    <row r="44" ht="14.25" customHeight="1"/>
-    <row r="45" ht="14.25" customHeight="1"/>
-    <row r="46" ht="14.25" customHeight="1"/>
-    <row r="47" ht="14.25" customHeight="1"/>
-    <row r="48" ht="14.25" customHeight="1"/>
-    <row r="49" ht="14.25" customHeight="1"/>
-    <row r="50" ht="14.25" customHeight="1"/>
-    <row r="51" ht="14.25" customHeight="1"/>
-    <row r="52" ht="14.25" customHeight="1"/>
-    <row r="53" ht="14.25" customHeight="1"/>
-    <row r="54" ht="14.25" customHeight="1"/>
-    <row r="55" ht="14.25" customHeight="1"/>
-    <row r="56" ht="14.25" customHeight="1"/>
-    <row r="57" ht="14.25" customHeight="1"/>
-    <row r="58" ht="14.25" customHeight="1"/>
-    <row r="59" ht="14.25" customHeight="1"/>
-    <row r="60" ht="14.25" customHeight="1"/>
-    <row r="61" ht="14.25" customHeight="1"/>
-    <row r="62" ht="14.25" customHeight="1"/>
-    <row r="63" ht="14.25" customHeight="1"/>
-    <row r="64" ht="14.25" customHeight="1"/>
-    <row r="65" ht="14.25" customHeight="1"/>
-    <row r="66" ht="14.25" customHeight="1"/>
-    <row r="67" ht="14.25" customHeight="1"/>
-    <row r="68" ht="14.25" customHeight="1"/>
-    <row r="69" ht="14.25" customHeight="1"/>
-    <row r="70" ht="14.25" customHeight="1"/>
-    <row r="71" ht="14.25" customHeight="1"/>
-    <row r="72" ht="14.25" customHeight="1"/>
-    <row r="73" ht="14.25" customHeight="1"/>
-    <row r="74" ht="14.25" customHeight="1"/>
-    <row r="75" ht="14.25" customHeight="1"/>
-    <row r="76" ht="14.25" customHeight="1"/>
-    <row r="77" ht="14.25" customHeight="1"/>
-    <row r="78" ht="14.25" customHeight="1"/>
-    <row r="79" ht="14.25" customHeight="1"/>
-    <row r="80" ht="14.25" customHeight="1"/>
-    <row r="81" ht="14.25" customHeight="1"/>
-    <row r="82" ht="14.25" customHeight="1"/>
-    <row r="83" ht="14.25" customHeight="1"/>
-    <row r="84" ht="14.25" customHeight="1"/>
-    <row r="85" ht="14.25" customHeight="1"/>
-    <row r="86" ht="14.25" customHeight="1"/>
-    <row r="87" ht="14.25" customHeight="1"/>
-    <row r="88" ht="14.25" customHeight="1"/>
-    <row r="89" ht="14.25" customHeight="1"/>
-    <row r="90" ht="14.25" customHeight="1"/>
-    <row r="91" ht="14.25" customHeight="1"/>
-    <row r="92" ht="14.25" customHeight="1"/>
-    <row r="93" ht="14.25" customHeight="1"/>
-    <row r="94" ht="14.25" customHeight="1"/>
-    <row r="95" ht="14.25" customHeight="1"/>
-    <row r="96" ht="14.25" customHeight="1"/>
-    <row r="97" ht="14.25" customHeight="1"/>
-    <row r="98" ht="14.25" customHeight="1"/>
-    <row r="99" ht="14.25" customHeight="1"/>
-    <row r="100" ht="14.25" customHeight="1"/>
-    <row r="101" ht="14.25" customHeight="1"/>
-    <row r="102" ht="14.25" customHeight="1"/>
-    <row r="103" ht="14.25" customHeight="1"/>
-    <row r="104" ht="14.25" customHeight="1"/>
-    <row r="105" ht="14.25" customHeight="1"/>
-    <row r="106" ht="14.25" customHeight="1"/>
-    <row r="107" ht="14.25" customHeight="1"/>
-    <row r="108" ht="14.25" customHeight="1"/>
-    <row r="109" ht="14.25" customHeight="1"/>
-    <row r="110" ht="14.25" customHeight="1"/>
-    <row r="111" ht="14.25" customHeight="1"/>
-    <row r="112" ht="14.25" customHeight="1"/>
-    <row r="113" ht="14.25" customHeight="1"/>
-    <row r="114" ht="14.25" customHeight="1"/>
-    <row r="115" ht="14.25" customHeight="1"/>
-    <row r="116" ht="14.25" customHeight="1"/>
-    <row r="117" ht="14.25" customHeight="1"/>
-    <row r="118" ht="14.25" customHeight="1"/>
-    <row r="119" ht="14.25" customHeight="1"/>
-    <row r="120" ht="14.25" customHeight="1"/>
-    <row r="121" ht="14.25" customHeight="1"/>
-    <row r="122" ht="14.25" customHeight="1"/>
-    <row r="123" ht="14.25" customHeight="1"/>
-    <row r="124" ht="14.25" customHeight="1"/>
-    <row r="125" ht="14.25" customHeight="1"/>
-    <row r="126" ht="14.25" customHeight="1"/>
-    <row r="127" ht="14.25" customHeight="1"/>
-    <row r="128" ht="14.25" customHeight="1"/>
-    <row r="129" ht="14.25" customHeight="1"/>
-    <row r="130" ht="14.25" customHeight="1"/>
-    <row r="131" ht="14.25" customHeight="1"/>
-    <row r="132" ht="14.25" customHeight="1"/>
-    <row r="133" ht="14.25" customHeight="1"/>
-    <row r="134" ht="14.25" customHeight="1"/>
-    <row r="135" ht="14.25" customHeight="1"/>
-    <row r="136" ht="14.25" customHeight="1"/>
-    <row r="137" ht="14.25" customHeight="1"/>
-    <row r="138" ht="14.25" customHeight="1"/>
-    <row r="139" ht="14.25" customHeight="1"/>
-    <row r="140" ht="14.25" customHeight="1"/>
-    <row r="141" ht="14.25" customHeight="1"/>
-    <row r="142" ht="14.25" customHeight="1"/>
-    <row r="143" ht="14.25" customHeight="1"/>
-    <row r="144" ht="14.25" customHeight="1"/>
-    <row r="145" ht="14.25" customHeight="1"/>
-    <row r="146" ht="14.25" customHeight="1"/>
-    <row r="147" ht="14.25" customHeight="1"/>
-    <row r="148" ht="14.25" customHeight="1"/>
-    <row r="149" ht="14.25" customHeight="1"/>
-    <row r="150" ht="14.25" customHeight="1"/>
-    <row r="151" ht="14.25" customHeight="1"/>
-    <row r="152" ht="14.25" customHeight="1"/>
-    <row r="153" ht="14.25" customHeight="1"/>
-    <row r="154" ht="14.25" customHeight="1"/>
-    <row r="155" ht="14.25" customHeight="1"/>
-    <row r="156" ht="14.25" customHeight="1"/>
-    <row r="157" ht="14.25" customHeight="1"/>
-    <row r="158" ht="14.25" customHeight="1"/>
-    <row r="159" ht="14.25" customHeight="1"/>
-    <row r="160" ht="14.25" customHeight="1"/>
-    <row r="161" ht="14.25" customHeight="1"/>
-    <row r="162" ht="14.25" customHeight="1"/>
-    <row r="163" ht="14.25" customHeight="1"/>
-    <row r="164" ht="14.25" customHeight="1"/>
-    <row r="165" ht="14.25" customHeight="1"/>
-    <row r="166" ht="14.25" customHeight="1"/>
-    <row r="167" ht="14.25" customHeight="1"/>
-    <row r="168" ht="14.25" customHeight="1"/>
-    <row r="169" ht="14.25" customHeight="1"/>
-    <row r="170" ht="14.25" customHeight="1"/>
-    <row r="171" ht="14.25" customHeight="1"/>
-    <row r="172" ht="14.25" customHeight="1"/>
-    <row r="173" ht="14.25" customHeight="1"/>
-    <row r="174" ht="14.25" customHeight="1"/>
-    <row r="175" ht="14.25" customHeight="1"/>
-    <row r="176" ht="14.25" customHeight="1"/>
-    <row r="177" ht="14.25" customHeight="1"/>
-    <row r="178" ht="14.25" customHeight="1"/>
-    <row r="179" ht="14.25" customHeight="1"/>
-    <row r="180" ht="14.25" customHeight="1"/>
-    <row r="181" ht="14.25" customHeight="1"/>
-    <row r="182" ht="14.25" customHeight="1"/>
-    <row r="183" ht="14.25" customHeight="1"/>
-    <row r="184" ht="14.25" customHeight="1"/>
-    <row r="185" ht="14.25" customHeight="1"/>
-    <row r="186" ht="14.25" customHeight="1"/>
-    <row r="187" ht="14.25" customHeight="1"/>
-    <row r="188" ht="14.25" customHeight="1"/>
-    <row r="189" ht="14.25" customHeight="1"/>
-    <row r="190" ht="14.25" customHeight="1"/>
-    <row r="191" ht="14.25" customHeight="1"/>
-    <row r="192" ht="14.25" customHeight="1"/>
-    <row r="193" ht="14.25" customHeight="1"/>
-    <row r="194" ht="14.25" customHeight="1"/>
-    <row r="195" ht="14.25" customHeight="1"/>
-    <row r="196" ht="14.25" customHeight="1"/>
-    <row r="197" ht="14.25" customHeight="1"/>
-    <row r="198" ht="14.25" customHeight="1"/>
-    <row r="199" ht="14.25" customHeight="1"/>
-    <row r="200" ht="14.25" customHeight="1"/>
-    <row r="201" ht="14.25" customHeight="1"/>
-    <row r="202" ht="14.25" customHeight="1"/>
-    <row r="203" ht="14.25" customHeight="1"/>
-    <row r="204" ht="14.25" customHeight="1"/>
-    <row r="205" ht="14.25" customHeight="1"/>
-    <row r="206" ht="14.25" customHeight="1"/>
-    <row r="207" ht="14.25" customHeight="1"/>
-    <row r="208" ht="14.25" customHeight="1"/>
-    <row r="209" ht="14.25" customHeight="1"/>
-    <row r="210" ht="14.25" customHeight="1"/>
-    <row r="211" ht="14.25" customHeight="1"/>
-    <row r="212" ht="14.25" customHeight="1"/>
-    <row r="213" ht="14.25" customHeight="1"/>
-    <row r="214" ht="14.25" customHeight="1"/>
-    <row r="215" ht="14.25" customHeight="1"/>
-    <row r="216" ht="14.25" customHeight="1"/>
-    <row r="217" ht="14.25" customHeight="1"/>
-    <row r="218" ht="14.25" customHeight="1"/>
-    <row r="219" ht="14.25" customHeight="1"/>
-    <row r="220" ht="14.25" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
-  </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>